--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6328,6 +6328,4060 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120141668</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>506672</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7114574</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120141680</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>506703</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7114470</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120141666</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>506960</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7115050</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120141687</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79608</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>506979</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7114590</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120141707</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>506822</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7114452</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120141678</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>506702</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7114515</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120141682</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>506688</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7114542</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120141705</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>506714</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7114740</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120141706</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>506637</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7114645</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120141691</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>506952</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7114997</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120141698</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>506955</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7114545</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120141673</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>506865</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7115101</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120141699</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>506982</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7114588</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120141672</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>506895</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7115116</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120141695</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>506750</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7114935</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120141704</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>506731</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7114940</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120141684</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>507001</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7114716</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120141697</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>506874</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7114372</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120141694</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>506824</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7114993</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120141675</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>506831</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7115012</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120141703</v>
+      </c>
+      <c r="B71" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>506664</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7114490</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120141709</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>506840</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7114370</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120141696</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>506756</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7114454</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120141710</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>506986</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7114613</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120141702</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>506729</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7114816</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120141692</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>506954</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7115013</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120141686</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79608</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>506978</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7114547</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120141677</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>506807</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7114959</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120141688</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>506908</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7114647</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120141701</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>506918</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7114686</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120141685</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79608</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>506955</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7114545</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120141667</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>506748</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7114878</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120141700</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>507032</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7114708</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120141671</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>507102</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7114733</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120141690</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>506952</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7114935</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120141689</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>506964</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7114937</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120141683</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>507001</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7114608</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120141681</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>506679</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7114465</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120141674</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stor-rishögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>506873</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7115121</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141668</v>
+        <v>120141700</v>
       </c>
       <c r="B51" t="n">
-        <v>90562</v>
+        <v>57421</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6342,38 +6342,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506672</v>
+        <v>507032</v>
       </c>
       <c r="R51" t="n">
-        <v>7114574</v>
+        <v>7114708</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6432,10 +6448,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141680</v>
+        <v>120141706</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,21 +6464,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6488,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506703</v>
+        <v>506637</v>
       </c>
       <c r="R52" t="n">
-        <v>7114470</v>
+        <v>7114645</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6508,11 +6524,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6539,10 +6550,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141666</v>
+        <v>120141671</v>
       </c>
       <c r="B53" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,21 +6566,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6579,10 +6590,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506960</v>
+        <v>507102</v>
       </c>
       <c r="R53" t="n">
-        <v>7115050</v>
+        <v>7114733</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6615,6 +6626,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6641,7 +6657,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141687</v>
+        <v>120141685</v>
       </c>
       <c r="B54" t="n">
         <v>79608</v>
@@ -6681,10 +6697,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506979</v>
+        <v>506955</v>
       </c>
       <c r="R54" t="n">
-        <v>7114590</v>
+        <v>7114545</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6743,10 +6759,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141707</v>
+        <v>120141666</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6759,21 +6775,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6783,10 +6799,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506822</v>
+        <v>506960</v>
       </c>
       <c r="R55" t="n">
-        <v>7114452</v>
+        <v>7115050</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6845,7 +6861,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141678</v>
+        <v>120141673</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6885,10 +6901,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506702</v>
+        <v>506865</v>
       </c>
       <c r="R56" t="n">
-        <v>7114515</v>
+        <v>7115101</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6925,7 +6941,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6952,10 +6968,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141682</v>
+        <v>120141668</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6968,21 +6984,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6992,10 +7008,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506688</v>
+        <v>506672</v>
       </c>
       <c r="R57" t="n">
-        <v>7114542</v>
+        <v>7114574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7028,11 +7044,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7059,10 +7070,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141705</v>
+        <v>120141683</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7075,21 +7086,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7099,10 +7110,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506714</v>
+        <v>507001</v>
       </c>
       <c r="R58" t="n">
-        <v>7114740</v>
+        <v>7114608</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7135,6 +7146,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7161,10 +7177,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141706</v>
+        <v>120141699</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7177,21 +7193,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7201,10 +7217,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506637</v>
+        <v>506982</v>
       </c>
       <c r="R59" t="n">
-        <v>7114645</v>
+        <v>7114588</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7263,10 +7279,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141691</v>
+        <v>120141705</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7279,21 +7295,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7303,10 +7319,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506952</v>
+        <v>506714</v>
       </c>
       <c r="R60" t="n">
-        <v>7114997</v>
+        <v>7114740</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7467,7 +7483,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141673</v>
+        <v>120141684</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7507,10 +7523,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506865</v>
+        <v>507001</v>
       </c>
       <c r="R62" t="n">
-        <v>7115101</v>
+        <v>7114716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7547,7 +7563,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7574,7 +7590,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141699</v>
+        <v>120141691</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7614,10 +7630,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506982</v>
+        <v>506952</v>
       </c>
       <c r="R63" t="n">
-        <v>7114588</v>
+        <v>7114997</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7676,7 +7692,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141672</v>
+        <v>120141680</v>
       </c>
       <c r="B64" t="n">
         <v>57310</v>
@@ -7716,10 +7732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506895</v>
+        <v>506703</v>
       </c>
       <c r="R64" t="n">
-        <v>7115116</v>
+        <v>7114470</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7756,7 +7772,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7783,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141695</v>
+        <v>120141701</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7799,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7823,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506750</v>
+        <v>506918</v>
       </c>
       <c r="R65" t="n">
-        <v>7114935</v>
+        <v>7114686</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7885,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141704</v>
+        <v>120141703</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7901,21 +7917,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7925,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506731</v>
+        <v>506664</v>
       </c>
       <c r="R66" t="n">
-        <v>7114940</v>
+        <v>7114490</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7987,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141684</v>
+        <v>120141709</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8003,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8027,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507001</v>
+        <v>506840</v>
       </c>
       <c r="R67" t="n">
-        <v>7114716</v>
+        <v>7114370</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8063,11 +8079,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8094,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141697</v>
+        <v>120141710</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8110,21 +8121,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8134,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506874</v>
+        <v>506986</v>
       </c>
       <c r="R68" t="n">
-        <v>7114372</v>
+        <v>7114613</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8298,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141675</v>
+        <v>120141695</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8314,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8338,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506831</v>
+        <v>506750</v>
       </c>
       <c r="R70" t="n">
-        <v>7115012</v>
+        <v>7114935</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8374,11 +8385,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8405,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141703</v>
+        <v>120141675</v>
       </c>
       <c r="B71" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8421,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8445,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506664</v>
+        <v>506831</v>
       </c>
       <c r="R71" t="n">
-        <v>7114490</v>
+        <v>7115012</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8481,6 +8487,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8507,10 +8518,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141709</v>
+        <v>120141674</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8523,21 +8534,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8547,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506840</v>
+        <v>506873</v>
       </c>
       <c r="R72" t="n">
-        <v>7114370</v>
+        <v>7115121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8583,6 +8594,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8609,10 +8625,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141696</v>
+        <v>120141678</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8625,21 +8641,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8649,10 +8665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506756</v>
+        <v>506702</v>
       </c>
       <c r="R73" t="n">
-        <v>7114454</v>
+        <v>7114515</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8685,6 +8701,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8711,10 +8732,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141710</v>
+        <v>120141682</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8727,21 +8748,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8751,10 +8772,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506986</v>
+        <v>506688</v>
       </c>
       <c r="R74" t="n">
-        <v>7114613</v>
+        <v>7114542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8787,6 +8808,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8813,10 +8839,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141702</v>
+        <v>120141667</v>
       </c>
       <c r="B75" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8829,21 +8855,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8853,10 +8879,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506729</v>
+        <v>506748</v>
       </c>
       <c r="R75" t="n">
-        <v>7114816</v>
+        <v>7114878</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8915,7 +8941,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141692</v>
+        <v>120141689</v>
       </c>
       <c r="B76" t="n">
         <v>79607</v>
@@ -8955,10 +8981,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506954</v>
+        <v>506964</v>
       </c>
       <c r="R76" t="n">
-        <v>7115013</v>
+        <v>7114937</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141686</v>
+        <v>120141672</v>
       </c>
       <c r="B77" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9033,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9057,10 +9083,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506978</v>
+        <v>506895</v>
       </c>
       <c r="R77" t="n">
-        <v>7114547</v>
+        <v>7115116</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9093,6 +9119,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9119,10 +9150,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141677</v>
+        <v>120141697</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9135,21 +9166,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9159,10 +9190,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506807</v>
+        <v>506874</v>
       </c>
       <c r="R78" t="n">
-        <v>7114959</v>
+        <v>7114372</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9195,11 +9226,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9328,10 +9354,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141701</v>
+        <v>120141707</v>
       </c>
       <c r="B80" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9344,21 +9370,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9368,10 +9394,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506918</v>
+        <v>506822</v>
       </c>
       <c r="R80" t="n">
-        <v>7114686</v>
+        <v>7114452</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9430,10 +9456,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141685</v>
+        <v>120141692</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9446,21 +9472,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9470,10 +9496,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506955</v>
+        <v>506954</v>
       </c>
       <c r="R81" t="n">
-        <v>7114545</v>
+        <v>7115013</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9532,10 +9558,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141667</v>
+        <v>120141704</v>
       </c>
       <c r="B82" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9548,21 +9574,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9572,10 +9598,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506748</v>
+        <v>506731</v>
       </c>
       <c r="R82" t="n">
-        <v>7114878</v>
+        <v>7114940</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9634,10 +9660,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141700</v>
+        <v>120141687</v>
       </c>
       <c r="B83" t="n">
-        <v>57421</v>
+        <v>79608</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9646,54 +9672,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>507032</v>
+        <v>506979</v>
       </c>
       <c r="R83" t="n">
-        <v>7114708</v>
+        <v>7114590</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9752,10 +9762,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141671</v>
+        <v>120141696</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9768,21 +9778,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9792,10 +9802,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>507102</v>
+        <v>506756</v>
       </c>
       <c r="R84" t="n">
-        <v>7114733</v>
+        <v>7114454</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9828,11 +9838,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9961,10 +9966,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141689</v>
+        <v>120141681</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9977,21 +9982,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10001,10 +10006,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506964</v>
+        <v>506679</v>
       </c>
       <c r="R86" t="n">
-        <v>7114937</v>
+        <v>7114465</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10037,6 +10042,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10063,7 +10073,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141683</v>
+        <v>120141677</v>
       </c>
       <c r="B87" t="n">
         <v>57310</v>
@@ -10103,10 +10113,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507001</v>
+        <v>506807</v>
       </c>
       <c r="R87" t="n">
-        <v>7114608</v>
+        <v>7114959</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10143,7 +10153,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10170,10 +10180,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141681</v>
+        <v>120141686</v>
       </c>
       <c r="B88" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10186,21 +10196,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10210,10 +10220,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506679</v>
+        <v>506978</v>
       </c>
       <c r="R88" t="n">
-        <v>7114465</v>
+        <v>7114547</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10246,11 +10256,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10277,10 +10282,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141674</v>
+        <v>120141702</v>
       </c>
       <c r="B89" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10293,21 +10298,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10317,10 +10322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506873</v>
+        <v>506729</v>
       </c>
       <c r="R89" t="n">
-        <v>7115121</v>
+        <v>7114816</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10353,11 +10358,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -7483,10 +7483,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141684</v>
+        <v>120141691</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7499,21 +7499,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507001</v>
+        <v>506952</v>
       </c>
       <c r="R62" t="n">
-        <v>7114716</v>
+        <v>7114997</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7559,11 +7559,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7590,10 +7585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141691</v>
+        <v>120141680</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7606,21 +7601,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7630,10 +7625,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506952</v>
+        <v>506703</v>
       </c>
       <c r="R63" t="n">
-        <v>7114997</v>
+        <v>7114470</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7666,6 +7661,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,7 +7692,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141680</v>
+        <v>120141684</v>
       </c>
       <c r="B64" t="n">
         <v>57310</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506703</v>
+        <v>507001</v>
       </c>
       <c r="R64" t="n">
-        <v>7114470</v>
+        <v>7114716</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8411,7 +8411,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141675</v>
+        <v>120141678</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506831</v>
+        <v>506702</v>
       </c>
       <c r="R71" t="n">
-        <v>7115012</v>
+        <v>7114515</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8518,7 +8518,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141674</v>
+        <v>120141675</v>
       </c>
       <c r="B72" t="n">
         <v>57310</v>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506873</v>
+        <v>506831</v>
       </c>
       <c r="R72" t="n">
-        <v>7115121</v>
+        <v>7115012</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8625,7 +8625,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141678</v>
+        <v>120141674</v>
       </c>
       <c r="B73" t="n">
         <v>57310</v>
@@ -8665,10 +8665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506702</v>
+        <v>506873</v>
       </c>
       <c r="R73" t="n">
-        <v>7114515</v>
+        <v>7115121</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141700</v>
+        <v>120141690</v>
       </c>
       <c r="B51" t="n">
-        <v>57421</v>
+        <v>79607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6342,54 +6342,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507032</v>
+        <v>506952</v>
       </c>
       <c r="R51" t="n">
-        <v>7114708</v>
+        <v>7114935</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6448,7 +6432,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141706</v>
+        <v>120141709</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6488,10 +6472,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506637</v>
+        <v>506840</v>
       </c>
       <c r="R52" t="n">
-        <v>7114645</v>
+        <v>7114370</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,10 +6534,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141671</v>
+        <v>120141687</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6566,21 +6550,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6590,10 +6574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507102</v>
+        <v>506979</v>
       </c>
       <c r="R53" t="n">
-        <v>7114733</v>
+        <v>7114590</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6626,11 +6610,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6657,10 +6636,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141685</v>
+        <v>120141673</v>
       </c>
       <c r="B54" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6673,21 +6652,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6697,10 +6676,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506955</v>
+        <v>506865</v>
       </c>
       <c r="R54" t="n">
-        <v>7114545</v>
+        <v>7115101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6733,6 +6712,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6759,10 +6743,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141666</v>
+        <v>120141699</v>
       </c>
       <c r="B55" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6775,21 +6759,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6799,10 +6783,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506960</v>
+        <v>506982</v>
       </c>
       <c r="R55" t="n">
-        <v>7115050</v>
+        <v>7114588</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6861,10 +6845,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141673</v>
+        <v>120141695</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6877,21 +6861,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6901,10 +6885,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506865</v>
+        <v>506750</v>
       </c>
       <c r="R56" t="n">
-        <v>7115101</v>
+        <v>7114935</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6937,11 +6921,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6968,10 +6947,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141668</v>
+        <v>120141694</v>
       </c>
       <c r="B57" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6984,21 +6963,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7008,10 +6987,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506672</v>
+        <v>506824</v>
       </c>
       <c r="R57" t="n">
-        <v>7114574</v>
+        <v>7114993</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7070,7 +7049,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141683</v>
+        <v>120141675</v>
       </c>
       <c r="B58" t="n">
         <v>57310</v>
@@ -7110,10 +7089,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507001</v>
+        <v>506831</v>
       </c>
       <c r="R58" t="n">
-        <v>7114608</v>
+        <v>7115012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7150,7 +7129,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7177,10 +7156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141699</v>
+        <v>120141678</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7193,21 +7172,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7217,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506982</v>
+        <v>506702</v>
       </c>
       <c r="R59" t="n">
-        <v>7114588</v>
+        <v>7114515</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7253,6 +7232,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7279,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141705</v>
+        <v>120141683</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7295,21 +7279,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7319,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506714</v>
+        <v>507001</v>
       </c>
       <c r="R60" t="n">
-        <v>7114740</v>
+        <v>7114608</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7355,6 +7339,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7381,10 +7370,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141698</v>
+        <v>120141667</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7397,21 +7386,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7421,10 +7410,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506955</v>
+        <v>506748</v>
       </c>
       <c r="R61" t="n">
-        <v>7114545</v>
+        <v>7114878</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7483,10 +7472,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141691</v>
+        <v>120141710</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7499,21 +7488,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7523,10 +7512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506952</v>
+        <v>506986</v>
       </c>
       <c r="R62" t="n">
-        <v>7114997</v>
+        <v>7114613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7585,10 +7574,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141680</v>
+        <v>120141700</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7597,20 +7586,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7618,17 +7607,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506703</v>
+        <v>507032</v>
       </c>
       <c r="R63" t="n">
-        <v>7114470</v>
+        <v>7114708</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7661,11 +7666,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7692,10 +7692,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141684</v>
+        <v>120141689</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507001</v>
+        <v>506964</v>
       </c>
       <c r="R64" t="n">
-        <v>7114716</v>
+        <v>7114937</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7768,11 +7768,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7799,7 +7794,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141701</v>
+        <v>120141702</v>
       </c>
       <c r="B65" t="n">
         <v>90580</v>
@@ -7839,10 +7834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506918</v>
+        <v>506729</v>
       </c>
       <c r="R65" t="n">
-        <v>7114686</v>
+        <v>7114816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141703</v>
+        <v>120141707</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7917,21 +7912,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7941,10 +7936,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506664</v>
+        <v>506822</v>
       </c>
       <c r="R66" t="n">
-        <v>7114490</v>
+        <v>7114452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +7998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141709</v>
+        <v>120141682</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8014,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8038,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506840</v>
+        <v>506688</v>
       </c>
       <c r="R67" t="n">
-        <v>7114370</v>
+        <v>7114542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8079,6 +8074,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141710</v>
+        <v>120141671</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8121,21 +8121,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506986</v>
+        <v>507102</v>
       </c>
       <c r="R68" t="n">
-        <v>7114613</v>
+        <v>7114733</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8181,6 +8181,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8207,7 +8212,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141694</v>
+        <v>120141698</v>
       </c>
       <c r="B69" t="n">
         <v>79607</v>
@@ -8247,10 +8252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506824</v>
+        <v>506955</v>
       </c>
       <c r="R69" t="n">
-        <v>7114993</v>
+        <v>7114545</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141695</v>
+        <v>120141706</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8325,21 +8330,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8349,10 +8354,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506750</v>
+        <v>506637</v>
       </c>
       <c r="R70" t="n">
-        <v>7114935</v>
+        <v>7114645</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8416,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141678</v>
+        <v>120141688</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8432,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8456,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506702</v>
+        <v>506908</v>
       </c>
       <c r="R71" t="n">
-        <v>7114515</v>
+        <v>7114647</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8487,11 +8492,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8518,10 +8518,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141675</v>
+        <v>120141685</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,21 +8534,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506831</v>
+        <v>506955</v>
       </c>
       <c r="R72" t="n">
-        <v>7115012</v>
+        <v>7114545</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8594,11 +8594,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8625,7 +8620,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141674</v>
+        <v>120141681</v>
       </c>
       <c r="B73" t="n">
         <v>57310</v>
@@ -8665,10 +8660,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506873</v>
+        <v>506679</v>
       </c>
       <c r="R73" t="n">
-        <v>7115121</v>
+        <v>7114465</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8732,7 +8727,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141682</v>
+        <v>120141680</v>
       </c>
       <c r="B74" t="n">
         <v>57310</v>
@@ -8772,10 +8767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506688</v>
+        <v>506703</v>
       </c>
       <c r="R74" t="n">
-        <v>7114542</v>
+        <v>7114470</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8812,7 +8807,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8839,10 +8834,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141667</v>
+        <v>120141674</v>
       </c>
       <c r="B75" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8855,21 +8850,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8879,10 +8874,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506748</v>
+        <v>506873</v>
       </c>
       <c r="R75" t="n">
-        <v>7114878</v>
+        <v>7115121</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8915,6 +8910,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8941,7 +8941,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141689</v>
+        <v>120141696</v>
       </c>
       <c r="B76" t="n">
         <v>79607</v>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506964</v>
+        <v>506756</v>
       </c>
       <c r="R76" t="n">
-        <v>7114937</v>
+        <v>7114454</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141672</v>
+        <v>120141668</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506895</v>
+        <v>506672</v>
       </c>
       <c r="R77" t="n">
-        <v>7115116</v>
+        <v>7114574</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,11 +9119,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9150,10 +9145,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141697</v>
+        <v>120141684</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9166,21 +9161,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9190,10 +9185,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506874</v>
+        <v>507001</v>
       </c>
       <c r="R78" t="n">
-        <v>7114372</v>
+        <v>7114716</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9226,6 +9221,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9252,10 +9252,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141688</v>
+        <v>120141686</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9268,21 +9268,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506908</v>
+        <v>506978</v>
       </c>
       <c r="R79" t="n">
-        <v>7114647</v>
+        <v>7114547</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9354,10 +9354,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141707</v>
+        <v>120141672</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9370,21 +9370,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506822</v>
+        <v>506895</v>
       </c>
       <c r="R80" t="n">
-        <v>7114452</v>
+        <v>7115116</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9430,6 +9430,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9456,10 +9461,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141692</v>
+        <v>120141677</v>
       </c>
       <c r="B81" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9472,21 +9477,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9496,10 +9501,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506954</v>
+        <v>506807</v>
       </c>
       <c r="R81" t="n">
-        <v>7115013</v>
+        <v>7114959</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9532,6 +9537,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9558,10 +9568,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141704</v>
+        <v>120141692</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9574,21 +9584,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9598,10 +9608,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506731</v>
+        <v>506954</v>
       </c>
       <c r="R82" t="n">
-        <v>7114940</v>
+        <v>7115013</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9660,10 +9670,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141687</v>
+        <v>120141705</v>
       </c>
       <c r="B83" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9676,21 +9686,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9700,10 +9710,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506979</v>
+        <v>506714</v>
       </c>
       <c r="R83" t="n">
-        <v>7114590</v>
+        <v>7114740</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9762,10 +9772,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141696</v>
+        <v>120141701</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9778,21 +9788,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9802,10 +9812,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506756</v>
+        <v>506918</v>
       </c>
       <c r="R84" t="n">
-        <v>7114454</v>
+        <v>7114686</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9864,10 +9874,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141690</v>
+        <v>120141666</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9880,21 +9890,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9904,10 +9914,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506952</v>
+        <v>506960</v>
       </c>
       <c r="R85" t="n">
-        <v>7114935</v>
+        <v>7115050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9966,10 +9976,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141681</v>
+        <v>120141691</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9982,21 +9992,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10006,10 +10016,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506679</v>
+        <v>506952</v>
       </c>
       <c r="R86" t="n">
-        <v>7114465</v>
+        <v>7114997</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10042,11 +10052,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10073,10 +10078,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141677</v>
+        <v>120141704</v>
       </c>
       <c r="B87" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10089,21 +10094,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10113,10 +10118,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506807</v>
+        <v>506731</v>
       </c>
       <c r="R87" t="n">
-        <v>7114959</v>
+        <v>7114940</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10149,11 +10154,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10180,10 +10180,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141686</v>
+        <v>120141697</v>
       </c>
       <c r="B88" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10196,21 +10196,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506978</v>
+        <v>506874</v>
       </c>
       <c r="R88" t="n">
-        <v>7114547</v>
+        <v>7114372</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10282,7 +10282,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141702</v>
+        <v>120141703</v>
       </c>
       <c r="B89" t="n">
         <v>90580</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506729</v>
+        <v>506664</v>
       </c>
       <c r="R89" t="n">
-        <v>7114816</v>
+        <v>7114490</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -7156,10 +7156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141678</v>
+        <v>120141667</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506702</v>
+        <v>506748</v>
       </c>
       <c r="R59" t="n">
-        <v>7114515</v>
+        <v>7114878</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7232,11 +7232,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7263,10 +7258,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141683</v>
+        <v>120141710</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7279,21 +7274,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7303,10 +7298,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507001</v>
+        <v>506986</v>
       </c>
       <c r="R60" t="n">
-        <v>7114608</v>
+        <v>7114613</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7339,11 +7334,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7370,10 +7360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141667</v>
+        <v>120141678</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7386,21 +7376,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506748</v>
+        <v>506702</v>
       </c>
       <c r="R61" t="n">
-        <v>7114878</v>
+        <v>7114515</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7446,6 +7436,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7472,10 +7467,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141710</v>
+        <v>120141683</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7488,21 +7483,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7512,10 +7507,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506986</v>
+        <v>507001</v>
       </c>
       <c r="R62" t="n">
-        <v>7114613</v>
+        <v>7114608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7548,6 +7543,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7794,10 +7794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141702</v>
+        <v>120141707</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7810,21 +7810,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506729</v>
+        <v>506822</v>
       </c>
       <c r="R65" t="n">
-        <v>7114816</v>
+        <v>7114452</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141707</v>
+        <v>120141702</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506822</v>
+        <v>506729</v>
       </c>
       <c r="R66" t="n">
-        <v>7114452</v>
+        <v>7114816</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141701</v>
+        <v>120141691</v>
       </c>
       <c r="B84" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9788,21 +9788,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9812,10 +9812,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506918</v>
+        <v>506952</v>
       </c>
       <c r="R84" t="n">
-        <v>7114686</v>
+        <v>7114997</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141666</v>
+        <v>120141701</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9890,21 +9890,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506960</v>
+        <v>506918</v>
       </c>
       <c r="R85" t="n">
-        <v>7115050</v>
+        <v>7114686</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9976,10 +9976,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141691</v>
+        <v>120141666</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9992,21 +9992,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506952</v>
+        <v>506960</v>
       </c>
       <c r="R86" t="n">
-        <v>7114997</v>
+        <v>7115050</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -7156,10 +7156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141667</v>
+        <v>120141678</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506748</v>
+        <v>506702</v>
       </c>
       <c r="R59" t="n">
-        <v>7114878</v>
+        <v>7114515</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7232,6 +7232,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7258,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141710</v>
+        <v>120141683</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7274,21 +7279,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7298,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506986</v>
+        <v>507001</v>
       </c>
       <c r="R60" t="n">
-        <v>7114613</v>
+        <v>7114608</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7334,6 +7339,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7360,10 +7370,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141678</v>
+        <v>120141667</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7376,21 +7386,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7400,10 +7410,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506702</v>
+        <v>506748</v>
       </c>
       <c r="R61" t="n">
-        <v>7114515</v>
+        <v>7114878</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7436,11 +7446,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7467,10 +7472,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141683</v>
+        <v>120141710</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,21 +7488,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7507,10 +7512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507001</v>
+        <v>506986</v>
       </c>
       <c r="R62" t="n">
-        <v>7114608</v>
+        <v>7114613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7543,11 +7548,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7794,10 +7794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141707</v>
+        <v>120141702</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7810,21 +7810,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506822</v>
+        <v>506729</v>
       </c>
       <c r="R65" t="n">
-        <v>7114452</v>
+        <v>7114816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141702</v>
+        <v>120141707</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506729</v>
+        <v>506822</v>
       </c>
       <c r="R66" t="n">
-        <v>7114816</v>
+        <v>7114452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -9772,10 +9772,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141691</v>
+        <v>120141701</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9788,21 +9788,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9812,10 +9812,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506952</v>
+        <v>506918</v>
       </c>
       <c r="R84" t="n">
-        <v>7114997</v>
+        <v>7114686</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141701</v>
+        <v>120141666</v>
       </c>
       <c r="B85" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9890,21 +9890,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506918</v>
+        <v>506960</v>
       </c>
       <c r="R85" t="n">
-        <v>7114686</v>
+        <v>7115050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9976,10 +9976,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141666</v>
+        <v>120141691</v>
       </c>
       <c r="B86" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9992,21 +9992,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506960</v>
+        <v>506952</v>
       </c>
       <c r="R86" t="n">
-        <v>7115050</v>
+        <v>7114997</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -7794,10 +7794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141702</v>
+        <v>120141707</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7810,21 +7810,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506729</v>
+        <v>506822</v>
       </c>
       <c r="R65" t="n">
-        <v>7114816</v>
+        <v>7114452</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141707</v>
+        <v>120141702</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506822</v>
+        <v>506729</v>
       </c>
       <c r="R66" t="n">
-        <v>7114452</v>
+        <v>7114816</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141685</v>
+        <v>120141681</v>
       </c>
       <c r="B72" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,21 +8534,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506955</v>
+        <v>506679</v>
       </c>
       <c r="R72" t="n">
-        <v>7114545</v>
+        <v>7114465</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8594,6 +8594,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8620,7 +8625,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141681</v>
+        <v>120141680</v>
       </c>
       <c r="B73" t="n">
         <v>57310</v>
@@ -8660,10 +8665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506679</v>
+        <v>506703</v>
       </c>
       <c r="R73" t="n">
-        <v>7114465</v>
+        <v>7114470</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8727,7 +8732,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141680</v>
+        <v>120141674</v>
       </c>
       <c r="B74" t="n">
         <v>57310</v>
@@ -8767,10 +8772,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506703</v>
+        <v>506873</v>
       </c>
       <c r="R74" t="n">
-        <v>7114470</v>
+        <v>7115121</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8834,10 +8839,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141674</v>
+        <v>120141685</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8850,21 +8855,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8874,10 +8879,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506873</v>
+        <v>506955</v>
       </c>
       <c r="R75" t="n">
-        <v>7115121</v>
+        <v>7114545</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8910,11 +8915,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141668</v>
+        <v>120141684</v>
       </c>
       <c r="B77" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506672</v>
+        <v>507001</v>
       </c>
       <c r="R77" t="n">
-        <v>7114574</v>
+        <v>7114716</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,6 +9119,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9145,10 +9150,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141684</v>
+        <v>120141668</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9161,21 +9166,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9185,10 +9190,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507001</v>
+        <v>506672</v>
       </c>
       <c r="R78" t="n">
-        <v>7114716</v>
+        <v>7114574</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9221,11 +9226,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9772,10 +9772,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141701</v>
+        <v>120141691</v>
       </c>
       <c r="B84" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9788,21 +9788,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9812,10 +9812,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506918</v>
+        <v>506952</v>
       </c>
       <c r="R84" t="n">
-        <v>7114686</v>
+        <v>7114997</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141666</v>
+        <v>120141701</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9890,21 +9890,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506960</v>
+        <v>506918</v>
       </c>
       <c r="R85" t="n">
-        <v>7115050</v>
+        <v>7114686</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9976,10 +9976,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141691</v>
+        <v>120141666</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9992,21 +9992,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506952</v>
+        <v>506960</v>
       </c>
       <c r="R86" t="n">
-        <v>7114997</v>
+        <v>7115050</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -7156,10 +7156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141678</v>
+        <v>120141667</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506702</v>
+        <v>506748</v>
       </c>
       <c r="R59" t="n">
-        <v>7114515</v>
+        <v>7114878</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7232,11 +7232,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7263,10 +7258,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141683</v>
+        <v>120141710</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7279,21 +7274,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7303,10 +7298,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507001</v>
+        <v>506986</v>
       </c>
       <c r="R60" t="n">
-        <v>7114608</v>
+        <v>7114613</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7339,11 +7334,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7370,10 +7360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141667</v>
+        <v>120141678</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7386,21 +7376,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506748</v>
+        <v>506702</v>
       </c>
       <c r="R61" t="n">
-        <v>7114878</v>
+        <v>7114515</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7446,6 +7436,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7472,10 +7467,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141710</v>
+        <v>120141683</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7488,21 +7483,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7512,10 +7507,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506986</v>
+        <v>507001</v>
       </c>
       <c r="R62" t="n">
-        <v>7114613</v>
+        <v>7114608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7548,6 +7543,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141684</v>
+        <v>120141668</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507001</v>
+        <v>506672</v>
       </c>
       <c r="R77" t="n">
-        <v>7114716</v>
+        <v>7114574</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,11 +9119,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9150,10 +9145,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141668</v>
+        <v>120141684</v>
       </c>
       <c r="B78" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9166,21 +9161,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9190,10 +9185,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506672</v>
+        <v>507001</v>
       </c>
       <c r="R78" t="n">
-        <v>7114574</v>
+        <v>7114716</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9226,6 +9221,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -7156,10 +7156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141667</v>
+        <v>120141678</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506748</v>
+        <v>506702</v>
       </c>
       <c r="R59" t="n">
-        <v>7114878</v>
+        <v>7114515</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7232,6 +7232,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7258,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141710</v>
+        <v>120141683</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7274,21 +7279,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7298,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506986</v>
+        <v>507001</v>
       </c>
       <c r="R60" t="n">
-        <v>7114613</v>
+        <v>7114608</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7334,6 +7339,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7360,10 +7370,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141678</v>
+        <v>120141667</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7376,21 +7386,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7400,10 +7410,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506702</v>
+        <v>506748</v>
       </c>
       <c r="R61" t="n">
-        <v>7114515</v>
+        <v>7114878</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7436,11 +7446,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7467,10 +7472,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141683</v>
+        <v>120141710</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,21 +7488,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7507,10 +7512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507001</v>
+        <v>506986</v>
       </c>
       <c r="R62" t="n">
-        <v>7114608</v>
+        <v>7114613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7543,11 +7548,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141668</v>
+        <v>120141684</v>
       </c>
       <c r="B77" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506672</v>
+        <v>507001</v>
       </c>
       <c r="R77" t="n">
-        <v>7114574</v>
+        <v>7114716</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,6 +9119,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9145,10 +9150,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141684</v>
+        <v>120141668</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9161,21 +9166,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9185,10 +9190,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507001</v>
+        <v>506672</v>
       </c>
       <c r="R78" t="n">
-        <v>7114716</v>
+        <v>7114574</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9221,11 +9226,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141690</v>
+        <v>120141685</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506952</v>
+        <v>506955</v>
       </c>
       <c r="R51" t="n">
-        <v>7114935</v>
+        <v>7114545</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141709</v>
+        <v>120141703</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,21 +6448,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506840</v>
+        <v>506664</v>
       </c>
       <c r="R52" t="n">
-        <v>7114370</v>
+        <v>7114490</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6534,10 +6534,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141687</v>
+        <v>120141674</v>
       </c>
       <c r="B53" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6550,21 +6550,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506979</v>
+        <v>506873</v>
       </c>
       <c r="R53" t="n">
-        <v>7114590</v>
+        <v>7115121</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6610,6 +6610,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6636,10 +6641,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141673</v>
+        <v>120141689</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6652,21 +6657,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6676,10 +6681,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506865</v>
+        <v>506964</v>
       </c>
       <c r="R54" t="n">
-        <v>7115101</v>
+        <v>7114937</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6712,11 +6717,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6743,10 +6743,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141699</v>
+        <v>120141690</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6783,10 +6783,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506982</v>
+        <v>506952</v>
       </c>
       <c r="R55" t="n">
-        <v>7114588</v>
+        <v>7114935</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141695</v>
+        <v>120141707</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6861,21 +6861,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506750</v>
+        <v>506822</v>
       </c>
       <c r="R56" t="n">
-        <v>7114935</v>
+        <v>7114452</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6947,10 +6947,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141694</v>
+        <v>120141696</v>
       </c>
       <c r="B57" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506824</v>
+        <v>506756</v>
       </c>
       <c r="R57" t="n">
-        <v>7114993</v>
+        <v>7114454</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141675</v>
+        <v>120141706</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7065,21 +7065,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506831</v>
+        <v>506637</v>
       </c>
       <c r="R58" t="n">
-        <v>7115012</v>
+        <v>7114645</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7125,11 +7125,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7156,10 +7151,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141678</v>
+        <v>120141671</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7196,10 +7191,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506702</v>
+        <v>507102</v>
       </c>
       <c r="R59" t="n">
-        <v>7114515</v>
+        <v>7114733</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7236,7 +7231,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7266,7 +7261,7 @@
         <v>120141683</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7370,10 +7365,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141667</v>
+        <v>120141673</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7386,21 +7381,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7410,10 +7405,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506748</v>
+        <v>506865</v>
       </c>
       <c r="R61" t="n">
-        <v>7114878</v>
+        <v>7115101</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7446,6 +7441,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7472,10 +7472,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141710</v>
+        <v>120141701</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7488,21 +7488,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506986</v>
+        <v>506918</v>
       </c>
       <c r="R62" t="n">
-        <v>7114613</v>
+        <v>7114686</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7577,7 +7577,7 @@
         <v>120141700</v>
       </c>
       <c r="B63" t="n">
-        <v>57421</v>
+        <v>57431</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7692,10 +7692,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141689</v>
+        <v>120141699</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506964</v>
+        <v>506982</v>
       </c>
       <c r="R64" t="n">
-        <v>7114937</v>
+        <v>7114588</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141707</v>
+        <v>120141704</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506822</v>
+        <v>506731</v>
       </c>
       <c r="R65" t="n">
-        <v>7114452</v>
+        <v>7114940</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141702</v>
+        <v>120141667</v>
       </c>
       <c r="B66" t="n">
         <v>90580</v>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506729</v>
+        <v>506748</v>
       </c>
       <c r="R66" t="n">
-        <v>7114816</v>
+        <v>7114878</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141682</v>
+        <v>120141709</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506688</v>
+        <v>506840</v>
       </c>
       <c r="R67" t="n">
-        <v>7114542</v>
+        <v>7114370</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8074,11 +8074,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8105,10 +8100,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141671</v>
+        <v>120141691</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8121,21 +8116,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8145,10 +8140,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507102</v>
+        <v>506952</v>
       </c>
       <c r="R68" t="n">
-        <v>7114733</v>
+        <v>7114997</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8181,11 +8176,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8212,10 +8202,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141698</v>
+        <v>120141710</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8228,21 +8218,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8252,10 +8242,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506955</v>
+        <v>506986</v>
       </c>
       <c r="R69" t="n">
-        <v>7114545</v>
+        <v>7114613</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8314,10 +8304,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141706</v>
+        <v>120141681</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8330,21 +8320,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8354,10 +8344,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506637</v>
+        <v>506679</v>
       </c>
       <c r="R70" t="n">
-        <v>7114645</v>
+        <v>7114465</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,6 +8380,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8416,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141688</v>
+        <v>120141678</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8432,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506908</v>
+        <v>506702</v>
       </c>
       <c r="R71" t="n">
-        <v>7114647</v>
+        <v>7114515</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8492,6 +8487,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8518,10 +8518,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141681</v>
+        <v>120141668</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,21 +8534,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506679</v>
+        <v>506672</v>
       </c>
       <c r="R72" t="n">
-        <v>7114465</v>
+        <v>7114574</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8594,11 +8594,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8625,10 +8620,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141680</v>
+        <v>120141692</v>
       </c>
       <c r="B73" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8641,21 +8636,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8665,10 +8660,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506703</v>
+        <v>506954</v>
       </c>
       <c r="R73" t="n">
-        <v>7114470</v>
+        <v>7115013</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8701,11 +8696,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8732,10 +8722,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141674</v>
+        <v>120141686</v>
       </c>
       <c r="B74" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8748,21 +8738,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8772,10 +8762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506873</v>
+        <v>506978</v>
       </c>
       <c r="R74" t="n">
-        <v>7115121</v>
+        <v>7114547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8808,11 +8798,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8839,10 +8824,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141685</v>
+        <v>120141675</v>
       </c>
       <c r="B75" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8855,21 +8840,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8879,10 +8864,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506955</v>
+        <v>506831</v>
       </c>
       <c r="R75" t="n">
-        <v>7114545</v>
+        <v>7115012</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8915,6 +8900,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8941,10 +8931,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141696</v>
+        <v>120141682</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8957,21 +8947,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8981,10 +8971,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506756</v>
+        <v>506688</v>
       </c>
       <c r="R76" t="n">
-        <v>7114454</v>
+        <v>7114542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,6 +9007,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9043,10 +9038,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141684</v>
+        <v>120141695</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9054,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9078,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507001</v>
+        <v>506750</v>
       </c>
       <c r="R77" t="n">
-        <v>7114716</v>
+        <v>7114935</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,11 +9114,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9150,10 +9140,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141668</v>
+        <v>120141697</v>
       </c>
       <c r="B78" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9166,21 +9156,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9190,10 +9180,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506672</v>
+        <v>506874</v>
       </c>
       <c r="R78" t="n">
-        <v>7114574</v>
+        <v>7114372</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9252,10 +9242,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141686</v>
+        <v>120141677</v>
       </c>
       <c r="B79" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9268,21 +9258,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9292,10 +9282,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506978</v>
+        <v>506807</v>
       </c>
       <c r="R79" t="n">
-        <v>7114547</v>
+        <v>7114959</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9328,6 +9318,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9354,10 +9349,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141672</v>
+        <v>120141694</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9370,21 +9365,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9394,10 +9389,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506895</v>
+        <v>506824</v>
       </c>
       <c r="R80" t="n">
-        <v>7115116</v>
+        <v>7114993</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9430,11 +9425,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9461,10 +9451,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141677</v>
+        <v>120141687</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9477,21 +9467,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9501,10 +9491,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506807</v>
+        <v>506979</v>
       </c>
       <c r="R81" t="n">
-        <v>7114959</v>
+        <v>7114590</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9537,11 +9527,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9568,10 +9553,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141692</v>
+        <v>120141705</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9584,21 +9569,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9608,10 +9593,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506954</v>
+        <v>506714</v>
       </c>
       <c r="R82" t="n">
-        <v>7115013</v>
+        <v>7114740</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9670,10 +9655,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141705</v>
+        <v>120141698</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9686,21 +9671,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9710,10 +9695,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506714</v>
+        <v>506955</v>
       </c>
       <c r="R83" t="n">
-        <v>7114740</v>
+        <v>7114545</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9772,10 +9757,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141691</v>
+        <v>120141688</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9812,10 +9797,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506952</v>
+        <v>506908</v>
       </c>
       <c r="R84" t="n">
-        <v>7114997</v>
+        <v>7114647</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9874,7 +9859,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141701</v>
+        <v>120141666</v>
       </c>
       <c r="B85" t="n">
         <v>90580</v>
@@ -9890,21 +9875,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9914,10 +9899,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506918</v>
+        <v>506960</v>
       </c>
       <c r="R85" t="n">
-        <v>7114686</v>
+        <v>7115050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9976,10 +9961,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141666</v>
+        <v>120141672</v>
       </c>
       <c r="B86" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9992,21 +9977,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10016,10 +10001,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506960</v>
+        <v>506895</v>
       </c>
       <c r="R86" t="n">
-        <v>7115050</v>
+        <v>7115116</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10052,6 +10037,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10078,10 +10068,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141704</v>
+        <v>120141680</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10094,21 +10084,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10118,10 +10108,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506731</v>
+        <v>506703</v>
       </c>
       <c r="R87" t="n">
-        <v>7114940</v>
+        <v>7114470</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10154,6 +10144,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10180,10 +10175,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141697</v>
+        <v>120141702</v>
       </c>
       <c r="B88" t="n">
-        <v>79607</v>
+        <v>90598</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10196,21 +10191,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10220,10 +10215,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506874</v>
+        <v>506729</v>
       </c>
       <c r="R88" t="n">
-        <v>7114372</v>
+        <v>7114816</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10282,10 +10277,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141703</v>
+        <v>120141684</v>
       </c>
       <c r="B89" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10298,21 +10293,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10322,10 +10317,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506664</v>
+        <v>507001</v>
       </c>
       <c r="R89" t="n">
-        <v>7114490</v>
+        <v>7114716</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10358,6 +10353,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141685</v>
+        <v>120141672</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506955</v>
+        <v>506895</v>
       </c>
       <c r="R51" t="n">
-        <v>7114545</v>
+        <v>7115116</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6406,6 +6406,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6432,10 +6437,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141703</v>
+        <v>120141675</v>
       </c>
       <c r="B52" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,21 +6453,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6477,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506664</v>
+        <v>506831</v>
       </c>
       <c r="R52" t="n">
-        <v>7114490</v>
+        <v>7115012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6508,6 +6513,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6534,10 +6544,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141674</v>
+        <v>120141686</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6550,21 +6560,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6574,10 +6584,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506873</v>
+        <v>506978</v>
       </c>
       <c r="R53" t="n">
-        <v>7115121</v>
+        <v>7114547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6610,11 +6620,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6641,7 +6646,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141689</v>
+        <v>120141699</v>
       </c>
       <c r="B54" t="n">
         <v>79623</v>
@@ -6681,10 +6686,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506964</v>
+        <v>506982</v>
       </c>
       <c r="R54" t="n">
-        <v>7114937</v>
+        <v>7114588</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6743,7 +6748,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141690</v>
+        <v>120141698</v>
       </c>
       <c r="B55" t="n">
         <v>79623</v>
@@ -6783,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506952</v>
+        <v>506955</v>
       </c>
       <c r="R55" t="n">
-        <v>7114935</v>
+        <v>7114545</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6845,10 +6850,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141707</v>
+        <v>120141694</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6861,21 +6866,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6885,10 +6890,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506822</v>
+        <v>506824</v>
       </c>
       <c r="R56" t="n">
-        <v>7114452</v>
+        <v>7114993</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6947,10 +6952,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141696</v>
+        <v>120141678</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6963,21 +6968,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6987,10 +6992,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506756</v>
+        <v>506702</v>
       </c>
       <c r="R57" t="n">
-        <v>7114454</v>
+        <v>7114515</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7023,6 +7028,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7049,7 +7059,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141706</v>
+        <v>120141709</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -7089,10 +7099,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506637</v>
+        <v>506840</v>
       </c>
       <c r="R58" t="n">
-        <v>7114645</v>
+        <v>7114370</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7151,10 +7161,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141671</v>
+        <v>120141692</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7167,21 +7177,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507102</v>
+        <v>506954</v>
       </c>
       <c r="R59" t="n">
-        <v>7114733</v>
+        <v>7115013</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7227,11 +7237,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7258,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141683</v>
+        <v>120141696</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7274,21 +7279,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7298,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507001</v>
+        <v>506756</v>
       </c>
       <c r="R60" t="n">
-        <v>7114608</v>
+        <v>7114454</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7334,11 +7339,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7365,10 +7365,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141673</v>
+        <v>120141689</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7381,21 +7381,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506865</v>
+        <v>506964</v>
       </c>
       <c r="R61" t="n">
-        <v>7115101</v>
+        <v>7114937</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7441,11 +7441,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7472,10 +7467,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141701</v>
+        <v>120141695</v>
       </c>
       <c r="B62" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7488,21 +7483,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7512,10 +7507,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506918</v>
+        <v>506750</v>
       </c>
       <c r="R62" t="n">
-        <v>7114686</v>
+        <v>7114935</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7574,10 +7569,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141700</v>
+        <v>120141707</v>
       </c>
       <c r="B63" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7586,54 +7581,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507032</v>
+        <v>506822</v>
       </c>
       <c r="R63" t="n">
-        <v>7114708</v>
+        <v>7114452</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7692,10 +7671,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141699</v>
+        <v>120141680</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7708,21 +7687,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7732,10 +7711,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506982</v>
+        <v>506703</v>
       </c>
       <c r="R64" t="n">
-        <v>7114588</v>
+        <v>7114470</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7768,6 +7747,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7794,10 +7778,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141704</v>
+        <v>120141701</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7810,21 +7794,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7834,10 +7818,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506731</v>
+        <v>506918</v>
       </c>
       <c r="R65" t="n">
-        <v>7114940</v>
+        <v>7114686</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7896,10 +7880,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141667</v>
+        <v>120141690</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7912,21 +7896,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7936,10 +7920,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506748</v>
+        <v>506952</v>
       </c>
       <c r="R66" t="n">
-        <v>7114878</v>
+        <v>7114935</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7998,10 +7982,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141709</v>
+        <v>120141681</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8014,21 +7998,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8038,10 +8022,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506840</v>
+        <v>506679</v>
       </c>
       <c r="R67" t="n">
-        <v>7114370</v>
+        <v>7114465</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8074,6 +8058,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8100,10 +8089,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141691</v>
+        <v>120141673</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8116,21 +8105,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8140,10 +8129,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506952</v>
+        <v>506865</v>
       </c>
       <c r="R68" t="n">
-        <v>7114997</v>
+        <v>7115101</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8176,6 +8165,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8202,7 +8196,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141710</v>
+        <v>120141706</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -8242,10 +8236,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506986</v>
+        <v>506637</v>
       </c>
       <c r="R69" t="n">
-        <v>7114613</v>
+        <v>7114645</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8304,10 +8298,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141681</v>
+        <v>120141688</v>
       </c>
       <c r="B70" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8320,21 +8314,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8344,10 +8338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506679</v>
+        <v>506908</v>
       </c>
       <c r="R70" t="n">
-        <v>7114465</v>
+        <v>7114647</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8380,11 +8374,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8411,10 +8400,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141678</v>
+        <v>120141668</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8416,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8440,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506702</v>
+        <v>506672</v>
       </c>
       <c r="R71" t="n">
-        <v>7114515</v>
+        <v>7114574</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8487,11 +8476,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8518,10 +8502,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141668</v>
+        <v>120141671</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,21 +8518,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8558,10 +8542,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506672</v>
+        <v>507102</v>
       </c>
       <c r="R72" t="n">
-        <v>7114574</v>
+        <v>7114733</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8594,6 +8578,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8620,10 +8609,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141692</v>
+        <v>120141687</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8636,21 +8625,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8660,10 +8649,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506954</v>
+        <v>506979</v>
       </c>
       <c r="R73" t="n">
-        <v>7115013</v>
+        <v>7114590</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8722,10 +8711,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141686</v>
+        <v>120141684</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8738,21 +8727,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8762,10 +8751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506978</v>
+        <v>507001</v>
       </c>
       <c r="R74" t="n">
-        <v>7114547</v>
+        <v>7114716</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8798,6 +8787,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8824,10 +8818,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141675</v>
+        <v>120141702</v>
       </c>
       <c r="B75" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8840,21 +8834,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8864,10 +8858,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506831</v>
+        <v>506729</v>
       </c>
       <c r="R75" t="n">
-        <v>7115012</v>
+        <v>7114816</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8900,11 +8894,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8931,10 +8920,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141682</v>
+        <v>120141703</v>
       </c>
       <c r="B76" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8947,21 +8936,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8971,10 +8960,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506688</v>
+        <v>506664</v>
       </c>
       <c r="R76" t="n">
-        <v>7114542</v>
+        <v>7114490</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9007,11 +8996,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9038,10 +9022,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141695</v>
+        <v>120141705</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9054,21 +9038,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9078,10 +9062,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506750</v>
+        <v>506714</v>
       </c>
       <c r="R77" t="n">
-        <v>7114935</v>
+        <v>7114740</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9242,10 +9226,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141677</v>
+        <v>120141704</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9258,21 +9242,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9282,10 +9266,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506807</v>
+        <v>506731</v>
       </c>
       <c r="R79" t="n">
-        <v>7114959</v>
+        <v>7114940</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9318,11 +9302,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9349,10 +9328,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141694</v>
+        <v>120141677</v>
       </c>
       <c r="B80" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9365,21 +9344,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9389,10 +9368,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506824</v>
+        <v>506807</v>
       </c>
       <c r="R80" t="n">
-        <v>7114993</v>
+        <v>7114959</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9425,6 +9404,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9451,10 +9435,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141687</v>
+        <v>120141683</v>
       </c>
       <c r="B81" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9467,21 +9451,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9491,10 +9475,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506979</v>
+        <v>507001</v>
       </c>
       <c r="R81" t="n">
-        <v>7114590</v>
+        <v>7114608</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9527,6 +9511,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9553,10 +9542,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141705</v>
+        <v>120141685</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9569,21 +9558,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9593,10 +9582,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506714</v>
+        <v>506955</v>
       </c>
       <c r="R82" t="n">
-        <v>7114740</v>
+        <v>7114545</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9655,10 +9644,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141698</v>
+        <v>120141666</v>
       </c>
       <c r="B83" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9671,21 +9660,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9695,10 +9684,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506955</v>
+        <v>506960</v>
       </c>
       <c r="R83" t="n">
-        <v>7114545</v>
+        <v>7115050</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9757,10 +9746,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141688</v>
+        <v>120141710</v>
       </c>
       <c r="B84" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9773,21 +9762,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9797,10 +9786,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506908</v>
+        <v>506986</v>
       </c>
       <c r="R84" t="n">
-        <v>7114647</v>
+        <v>7114613</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9859,7 +9848,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141666</v>
+        <v>120141667</v>
       </c>
       <c r="B85" t="n">
         <v>90580</v>
@@ -9899,10 +9888,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506960</v>
+        <v>506748</v>
       </c>
       <c r="R85" t="n">
-        <v>7115050</v>
+        <v>7114878</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9961,10 +9950,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141672</v>
+        <v>120141691</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9977,21 +9966,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10001,10 +9990,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506895</v>
+        <v>506952</v>
       </c>
       <c r="R86" t="n">
-        <v>7115116</v>
+        <v>7114997</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10037,11 +10026,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10068,10 +10052,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141680</v>
+        <v>120141700</v>
       </c>
       <c r="B87" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10080,20 +10064,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10101,17 +10085,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506703</v>
+        <v>507032</v>
       </c>
       <c r="R87" t="n">
-        <v>7114470</v>
+        <v>7114708</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10144,11 +10144,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10175,10 +10170,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141702</v>
+        <v>120141682</v>
       </c>
       <c r="B88" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10191,21 +10186,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10215,10 +10210,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506729</v>
+        <v>506688</v>
       </c>
       <c r="R88" t="n">
-        <v>7114816</v>
+        <v>7114542</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10251,6 +10246,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10277,7 +10277,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141684</v>
+        <v>120141674</v>
       </c>
       <c r="B89" t="n">
         <v>57320</v>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507001</v>
+        <v>506873</v>
       </c>
       <c r="R89" t="n">
-        <v>7114716</v>
+        <v>7115121</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141672</v>
+        <v>120141686</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506895</v>
+        <v>506978</v>
       </c>
       <c r="R51" t="n">
-        <v>7115116</v>
+        <v>7114547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6406,11 +6406,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6437,7 +6432,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141675</v>
+        <v>120141672</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506831</v>
+        <v>506895</v>
       </c>
       <c r="R52" t="n">
-        <v>7115012</v>
+        <v>7115116</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6517,7 +6512,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6544,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141686</v>
+        <v>120141675</v>
       </c>
       <c r="B53" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6560,21 +6555,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506978</v>
+        <v>506831</v>
       </c>
       <c r="R53" t="n">
-        <v>7114547</v>
+        <v>7115012</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6620,6 +6615,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -8400,10 +8400,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141668</v>
+        <v>120141687</v>
       </c>
       <c r="B71" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506672</v>
+        <v>506979</v>
       </c>
       <c r="R71" t="n">
-        <v>7114574</v>
+        <v>7114590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141671</v>
+        <v>120141668</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507102</v>
+        <v>506672</v>
       </c>
       <c r="R72" t="n">
-        <v>7114733</v>
+        <v>7114574</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8578,11 +8578,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8609,10 +8604,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141687</v>
+        <v>120141671</v>
       </c>
       <c r="B73" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8625,21 +8620,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8649,10 +8644,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506979</v>
+        <v>507102</v>
       </c>
       <c r="R73" t="n">
-        <v>7114590</v>
+        <v>7114733</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8685,6 +8680,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8711,10 +8711,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141684</v>
+        <v>120141702</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8727,21 +8727,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507001</v>
+        <v>506729</v>
       </c>
       <c r="R74" t="n">
-        <v>7114716</v>
+        <v>7114816</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8787,11 +8787,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8818,7 +8813,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141702</v>
+        <v>120141703</v>
       </c>
       <c r="B75" t="n">
         <v>90598</v>
@@ -8858,10 +8853,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506729</v>
+        <v>506664</v>
       </c>
       <c r="R75" t="n">
-        <v>7114816</v>
+        <v>7114490</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,10 +8915,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141703</v>
+        <v>120141684</v>
       </c>
       <c r="B76" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8936,21 +8931,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8960,10 +8955,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506664</v>
+        <v>507001</v>
       </c>
       <c r="R76" t="n">
-        <v>7114490</v>
+        <v>7114716</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8996,6 +8991,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9435,10 +9435,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141683</v>
+        <v>120141685</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9451,21 +9451,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507001</v>
+        <v>506955</v>
       </c>
       <c r="R81" t="n">
-        <v>7114608</v>
+        <v>7114545</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9511,11 +9511,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9542,10 +9537,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141685</v>
+        <v>120141683</v>
       </c>
       <c r="B82" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9558,21 +9553,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9582,10 +9577,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506955</v>
+        <v>507001</v>
       </c>
       <c r="R82" t="n">
-        <v>7114545</v>
+        <v>7114608</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9618,6 +9613,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9848,10 +9848,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141667</v>
+        <v>120141700</v>
       </c>
       <c r="B85" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9860,38 +9860,54 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506748</v>
+        <v>507032</v>
       </c>
       <c r="R85" t="n">
-        <v>7114878</v>
+        <v>7114708</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9950,10 +9966,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141691</v>
+        <v>120141667</v>
       </c>
       <c r="B86" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9966,21 +9982,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9990,10 +10006,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506952</v>
+        <v>506748</v>
       </c>
       <c r="R86" t="n">
-        <v>7114997</v>
+        <v>7114878</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10052,10 +10068,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141700</v>
+        <v>120141691</v>
       </c>
       <c r="B87" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10064,54 +10080,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507032</v>
+        <v>506952</v>
       </c>
       <c r="R87" t="n">
-        <v>7114708</v>
+        <v>7114997</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141686</v>
+        <v>120141701</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506978</v>
+        <v>506918</v>
       </c>
       <c r="R51" t="n">
-        <v>7114547</v>
+        <v>7114686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141672</v>
+        <v>120141689</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,21 +6448,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506895</v>
+        <v>506964</v>
       </c>
       <c r="R52" t="n">
-        <v>7115116</v>
+        <v>7114937</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6508,11 +6508,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6539,10 +6534,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141675</v>
+        <v>120141688</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,21 +6550,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6579,10 +6574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506831</v>
+        <v>506908</v>
       </c>
       <c r="R53" t="n">
-        <v>7115012</v>
+        <v>7114647</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6615,11 +6610,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6646,10 +6636,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141699</v>
+        <v>120141705</v>
       </c>
       <c r="B54" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6662,21 +6652,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6686,10 +6676,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506982</v>
+        <v>506714</v>
       </c>
       <c r="R54" t="n">
-        <v>7114588</v>
+        <v>7114740</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6748,10 +6738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141698</v>
+        <v>120141685</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6764,21 +6754,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6850,10 +6840,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141694</v>
+        <v>120141683</v>
       </c>
       <c r="B56" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6866,21 +6856,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6890,10 +6880,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506824</v>
+        <v>507001</v>
       </c>
       <c r="R56" t="n">
-        <v>7114993</v>
+        <v>7114608</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6926,6 +6916,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6952,7 +6947,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141678</v>
+        <v>120141681</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6992,10 +6987,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506702</v>
+        <v>506679</v>
       </c>
       <c r="R57" t="n">
-        <v>7114515</v>
+        <v>7114465</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7059,10 +7054,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141709</v>
+        <v>120141673</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7075,21 +7070,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7099,10 +7094,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506840</v>
+        <v>506865</v>
       </c>
       <c r="R58" t="n">
-        <v>7114370</v>
+        <v>7115101</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7135,6 +7130,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7161,10 +7161,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141692</v>
+        <v>120141668</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506954</v>
+        <v>506672</v>
       </c>
       <c r="R59" t="n">
-        <v>7115013</v>
+        <v>7114574</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141696</v>
+        <v>120141702</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7279,21 +7279,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506756</v>
+        <v>506729</v>
       </c>
       <c r="R60" t="n">
-        <v>7114454</v>
+        <v>7114816</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7365,10 +7365,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141689</v>
+        <v>120141703</v>
       </c>
       <c r="B61" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7381,21 +7381,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506964</v>
+        <v>506664</v>
       </c>
       <c r="R61" t="n">
-        <v>7114937</v>
+        <v>7114490</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141695</v>
+        <v>120141699</v>
       </c>
       <c r="B62" t="n">
         <v>79623</v>
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506750</v>
+        <v>506982</v>
       </c>
       <c r="R62" t="n">
-        <v>7114935</v>
+        <v>7114588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141707</v>
+        <v>120141684</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7585,21 +7585,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506822</v>
+        <v>507001</v>
       </c>
       <c r="R63" t="n">
-        <v>7114452</v>
+        <v>7114716</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7645,6 +7645,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7671,10 +7676,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141680</v>
+        <v>120141700</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7683,20 +7688,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7704,17 +7709,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506703</v>
+        <v>507032</v>
       </c>
       <c r="R64" t="n">
-        <v>7114470</v>
+        <v>7114708</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7747,11 +7768,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7778,10 +7794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141701</v>
+        <v>120141666</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7794,21 +7810,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7818,10 +7834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506918</v>
+        <v>506960</v>
       </c>
       <c r="R65" t="n">
-        <v>7114686</v>
+        <v>7115050</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7880,10 +7896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141690</v>
+        <v>120141706</v>
       </c>
       <c r="B66" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7896,21 +7912,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7920,10 +7936,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506952</v>
+        <v>506637</v>
       </c>
       <c r="R66" t="n">
-        <v>7114935</v>
+        <v>7114645</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7982,10 +7998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141681</v>
+        <v>120141710</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7998,21 +8014,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8022,10 +8038,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506679</v>
+        <v>506986</v>
       </c>
       <c r="R67" t="n">
-        <v>7114465</v>
+        <v>7114613</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8058,11 +8074,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8089,10 +8100,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141673</v>
+        <v>120141704</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8105,21 +8116,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8129,10 +8140,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506865</v>
+        <v>506731</v>
       </c>
       <c r="R68" t="n">
-        <v>7115101</v>
+        <v>7114940</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8165,11 +8176,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8196,10 +8202,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141706</v>
+        <v>120141671</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8212,21 +8218,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8236,10 +8242,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506637</v>
+        <v>507102</v>
       </c>
       <c r="R69" t="n">
-        <v>7114645</v>
+        <v>7114733</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8272,6 +8278,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8298,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141688</v>
+        <v>120141667</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8314,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8338,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506908</v>
+        <v>506748</v>
       </c>
       <c r="R70" t="n">
-        <v>7114647</v>
+        <v>7114878</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8502,10 +8513,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141668</v>
+        <v>120141672</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8518,21 +8529,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8542,10 +8553,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506672</v>
+        <v>506895</v>
       </c>
       <c r="R72" t="n">
-        <v>7114574</v>
+        <v>7115116</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8578,6 +8589,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8604,7 +8620,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141671</v>
+        <v>120141675</v>
       </c>
       <c r="B73" t="n">
         <v>57320</v>
@@ -8644,10 +8660,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507102</v>
+        <v>506831</v>
       </c>
       <c r="R73" t="n">
-        <v>7114733</v>
+        <v>7115012</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8684,7 +8700,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8711,10 +8727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141702</v>
+        <v>120141686</v>
       </c>
       <c r="B74" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8727,21 +8743,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8751,10 +8767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506729</v>
+        <v>506978</v>
       </c>
       <c r="R74" t="n">
-        <v>7114816</v>
+        <v>7114547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8813,10 +8829,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141703</v>
+        <v>120141691</v>
       </c>
       <c r="B75" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8829,21 +8845,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8853,10 +8869,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506664</v>
+        <v>506952</v>
       </c>
       <c r="R75" t="n">
-        <v>7114490</v>
+        <v>7114997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8915,10 +8931,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141684</v>
+        <v>120141692</v>
       </c>
       <c r="B76" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8931,21 +8947,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8955,10 +8971,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507001</v>
+        <v>506954</v>
       </c>
       <c r="R76" t="n">
-        <v>7114716</v>
+        <v>7115013</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8991,11 +9007,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9022,10 +9033,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141705</v>
+        <v>120141694</v>
       </c>
       <c r="B77" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9038,21 +9049,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9062,10 +9073,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506714</v>
+        <v>506824</v>
       </c>
       <c r="R77" t="n">
-        <v>7114740</v>
+        <v>7114993</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9124,10 +9135,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141697</v>
+        <v>120141674</v>
       </c>
       <c r="B78" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9140,21 +9151,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9164,10 +9175,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506874</v>
+        <v>506873</v>
       </c>
       <c r="R78" t="n">
-        <v>7114372</v>
+        <v>7115121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9200,6 +9211,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9226,10 +9242,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141704</v>
+        <v>120141696</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9242,21 +9258,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9266,10 +9282,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506731</v>
+        <v>506756</v>
       </c>
       <c r="R79" t="n">
-        <v>7114940</v>
+        <v>7114454</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9328,10 +9344,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141677</v>
+        <v>120141690</v>
       </c>
       <c r="B80" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9344,21 +9360,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9368,10 +9384,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506807</v>
+        <v>506952</v>
       </c>
       <c r="R80" t="n">
-        <v>7114959</v>
+        <v>7114935</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9404,11 +9420,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9435,10 +9446,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141685</v>
+        <v>120141707</v>
       </c>
       <c r="B81" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9451,21 +9462,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9475,10 +9486,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506955</v>
+        <v>506822</v>
       </c>
       <c r="R81" t="n">
-        <v>7114545</v>
+        <v>7114452</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9537,10 +9548,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141683</v>
+        <v>120141698</v>
       </c>
       <c r="B82" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9553,21 +9564,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9577,10 +9588,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>507001</v>
+        <v>506955</v>
       </c>
       <c r="R82" t="n">
-        <v>7114608</v>
+        <v>7114545</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9613,11 +9624,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9644,10 +9650,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141666</v>
+        <v>120141709</v>
       </c>
       <c r="B83" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9660,21 +9666,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9684,10 +9690,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506960</v>
+        <v>506840</v>
       </c>
       <c r="R83" t="n">
-        <v>7115050</v>
+        <v>7114370</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9746,10 +9752,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141710</v>
+        <v>120141678</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9762,21 +9768,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9786,10 +9792,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506986</v>
+        <v>506702</v>
       </c>
       <c r="R84" t="n">
-        <v>7114613</v>
+        <v>7114515</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9822,6 +9828,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9848,10 +9859,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141700</v>
+        <v>120141697</v>
       </c>
       <c r="B85" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9860,54 +9871,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507032</v>
+        <v>506874</v>
       </c>
       <c r="R85" t="n">
-        <v>7114708</v>
+        <v>7114372</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9966,10 +9961,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141667</v>
+        <v>120141682</v>
       </c>
       <c r="B86" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9982,21 +9977,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10006,10 +10001,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506748</v>
+        <v>506688</v>
       </c>
       <c r="R86" t="n">
-        <v>7114878</v>
+        <v>7114542</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10042,6 +10037,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10068,10 +10068,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141691</v>
+        <v>120141680</v>
       </c>
       <c r="B87" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10084,21 +10084,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506952</v>
+        <v>506703</v>
       </c>
       <c r="R87" t="n">
-        <v>7114997</v>
+        <v>7114470</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10144,6 +10144,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10170,7 +10175,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141682</v>
+        <v>120141677</v>
       </c>
       <c r="B88" t="n">
         <v>57320</v>
@@ -10210,10 +10215,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506688</v>
+        <v>506807</v>
       </c>
       <c r="R88" t="n">
-        <v>7114542</v>
+        <v>7114959</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10250,7 +10255,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10277,10 +10282,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141674</v>
+        <v>120141695</v>
       </c>
       <c r="B89" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10293,21 +10298,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10317,10 +10322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506873</v>
+        <v>506750</v>
       </c>
       <c r="R89" t="n">
-        <v>7115121</v>
+        <v>7114935</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10353,11 +10358,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -8100,10 +8100,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141704</v>
+        <v>120141671</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8116,21 +8116,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506731</v>
+        <v>507102</v>
       </c>
       <c r="R68" t="n">
-        <v>7114940</v>
+        <v>7114733</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8176,6 +8176,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8202,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141671</v>
+        <v>120141704</v>
       </c>
       <c r="B69" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8218,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8242,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507102</v>
+        <v>506731</v>
       </c>
       <c r="R69" t="n">
-        <v>7114733</v>
+        <v>7114940</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8278,11 +8283,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8727,10 +8727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141686</v>
+        <v>120141691</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8743,21 +8743,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8767,10 +8767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506978</v>
+        <v>506952</v>
       </c>
       <c r="R74" t="n">
-        <v>7114547</v>
+        <v>7114997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8829,10 +8829,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141691</v>
+        <v>120141686</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8845,21 +8845,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506952</v>
+        <v>506978</v>
       </c>
       <c r="R75" t="n">
-        <v>7114997</v>
+        <v>7114547</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9548,10 +9548,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141698</v>
+        <v>120141678</v>
       </c>
       <c r="B82" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9564,21 +9564,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506955</v>
+        <v>506702</v>
       </c>
       <c r="R82" t="n">
-        <v>7114545</v>
+        <v>7114515</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9624,6 +9624,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9650,10 +9655,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141709</v>
+        <v>120141698</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9666,21 +9671,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9690,10 +9695,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506840</v>
+        <v>506955</v>
       </c>
       <c r="R83" t="n">
-        <v>7114370</v>
+        <v>7114545</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9752,10 +9757,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141678</v>
+        <v>120141709</v>
       </c>
       <c r="B84" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9768,21 +9773,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9792,10 +9797,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506702</v>
+        <v>506840</v>
       </c>
       <c r="R84" t="n">
-        <v>7114515</v>
+        <v>7114370</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9828,11 +9833,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9961,10 +9961,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141682</v>
+        <v>120141695</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9977,21 +9977,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506688</v>
+        <v>506750</v>
       </c>
       <c r="R86" t="n">
-        <v>7114542</v>
+        <v>7114935</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10037,11 +10037,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10068,7 +10063,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141680</v>
+        <v>120141682</v>
       </c>
       <c r="B87" t="n">
         <v>57320</v>
@@ -10108,10 +10103,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506703</v>
+        <v>506688</v>
       </c>
       <c r="R87" t="n">
-        <v>7114470</v>
+        <v>7114542</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10148,7 +10143,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10175,7 +10170,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141677</v>
+        <v>120141680</v>
       </c>
       <c r="B88" t="n">
         <v>57320</v>
@@ -10215,10 +10210,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506807</v>
+        <v>506703</v>
       </c>
       <c r="R88" t="n">
-        <v>7114959</v>
+        <v>7114470</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10282,10 +10277,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141695</v>
+        <v>120141677</v>
       </c>
       <c r="B89" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10298,21 +10293,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10322,10 +10317,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506750</v>
+        <v>506807</v>
       </c>
       <c r="R89" t="n">
-        <v>7114935</v>
+        <v>7114959</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10358,6 +10353,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141701</v>
+        <v>120141700</v>
       </c>
       <c r="B51" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6342,38 +6342,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506918</v>
+        <v>507032</v>
       </c>
       <c r="R51" t="n">
-        <v>7114686</v>
+        <v>7114708</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6432,7 +6448,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141689</v>
+        <v>120141690</v>
       </c>
       <c r="B52" t="n">
         <v>79623</v>
@@ -6472,10 +6488,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506964</v>
+        <v>506952</v>
       </c>
       <c r="R52" t="n">
-        <v>7114937</v>
+        <v>7114935</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6534,10 +6550,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141688</v>
+        <v>120141710</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6550,21 +6566,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6574,10 +6590,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506908</v>
+        <v>506986</v>
       </c>
       <c r="R53" t="n">
-        <v>7114647</v>
+        <v>7114613</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6636,7 +6652,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141705</v>
+        <v>120141706</v>
       </c>
       <c r="B54" t="n">
         <v>78542</v>
@@ -6676,10 +6692,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506714</v>
+        <v>506637</v>
       </c>
       <c r="R54" t="n">
-        <v>7114740</v>
+        <v>7114645</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6738,10 +6754,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141685</v>
+        <v>120141707</v>
       </c>
       <c r="B55" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6754,21 +6770,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6778,10 +6794,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506955</v>
+        <v>506822</v>
       </c>
       <c r="R55" t="n">
-        <v>7114545</v>
+        <v>7114452</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6840,10 +6856,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141683</v>
+        <v>120141666</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6856,21 +6872,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6880,10 +6896,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507001</v>
+        <v>506960</v>
       </c>
       <c r="R56" t="n">
-        <v>7114608</v>
+        <v>7115050</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6916,11 +6932,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6947,7 +6958,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141681</v>
+        <v>120141671</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6987,10 +6998,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506679</v>
+        <v>507102</v>
       </c>
       <c r="R57" t="n">
-        <v>7114465</v>
+        <v>7114733</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7027,7 +7038,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7054,10 +7065,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141673</v>
+        <v>120141692</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7070,21 +7081,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7094,10 +7105,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506865</v>
+        <v>506954</v>
       </c>
       <c r="R58" t="n">
-        <v>7115101</v>
+        <v>7115013</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7130,11 +7141,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7161,10 +7167,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141668</v>
+        <v>120141709</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7177,21 +7183,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7201,10 +7207,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506672</v>
+        <v>506840</v>
       </c>
       <c r="R59" t="n">
-        <v>7114574</v>
+        <v>7114370</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7263,10 +7269,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141702</v>
+        <v>120141683</v>
       </c>
       <c r="B60" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7279,21 +7285,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7303,10 +7309,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506729</v>
+        <v>507001</v>
       </c>
       <c r="R60" t="n">
-        <v>7114816</v>
+        <v>7114608</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7339,6 +7345,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7365,10 +7376,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141703</v>
+        <v>120141682</v>
       </c>
       <c r="B61" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7381,21 +7392,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7405,10 +7416,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506664</v>
+        <v>506688</v>
       </c>
       <c r="R61" t="n">
-        <v>7114490</v>
+        <v>7114542</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7441,6 +7452,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7467,10 +7483,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141699</v>
+        <v>120141674</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,21 +7499,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7507,10 +7523,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506982</v>
+        <v>506873</v>
       </c>
       <c r="R62" t="n">
-        <v>7114588</v>
+        <v>7115121</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7543,6 +7559,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7569,7 +7590,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141684</v>
+        <v>120141675</v>
       </c>
       <c r="B63" t="n">
         <v>57320</v>
@@ -7609,10 +7630,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507001</v>
+        <v>506831</v>
       </c>
       <c r="R63" t="n">
-        <v>7114716</v>
+        <v>7115012</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7649,7 +7670,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7676,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141700</v>
+        <v>120141703</v>
       </c>
       <c r="B64" t="n">
-        <v>57431</v>
+        <v>90598</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7688,54 +7709,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507032</v>
+        <v>506664</v>
       </c>
       <c r="R64" t="n">
-        <v>7114708</v>
+        <v>7114490</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7794,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141666</v>
+        <v>120141691</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7810,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7834,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506960</v>
+        <v>506952</v>
       </c>
       <c r="R65" t="n">
-        <v>7115050</v>
+        <v>7114997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7896,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141706</v>
+        <v>120141673</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7912,21 +7917,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7936,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506637</v>
+        <v>506865</v>
       </c>
       <c r="R66" t="n">
-        <v>7114645</v>
+        <v>7115101</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7972,6 +7977,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7998,10 +8008,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141710</v>
+        <v>120141678</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8014,21 +8024,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8038,10 +8048,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506986</v>
+        <v>506702</v>
       </c>
       <c r="R67" t="n">
-        <v>7114613</v>
+        <v>7114515</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8074,6 +8084,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8100,10 +8115,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141671</v>
+        <v>120141698</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8116,21 +8131,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8140,10 +8155,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507102</v>
+        <v>506955</v>
       </c>
       <c r="R68" t="n">
-        <v>7114733</v>
+        <v>7114545</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8176,11 +8191,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8207,7 +8217,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141704</v>
+        <v>120141705</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -8247,10 +8257,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506731</v>
+        <v>506714</v>
       </c>
       <c r="R69" t="n">
-        <v>7114940</v>
+        <v>7114740</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8319,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141667</v>
+        <v>120141702</v>
       </c>
       <c r="B70" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8325,21 +8335,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8349,10 +8359,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506748</v>
+        <v>506729</v>
       </c>
       <c r="R70" t="n">
-        <v>7114878</v>
+        <v>7114816</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,7 +8421,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141687</v>
+        <v>120141685</v>
       </c>
       <c r="B71" t="n">
         <v>79624</v>
@@ -8451,10 +8461,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506979</v>
+        <v>506955</v>
       </c>
       <c r="R71" t="n">
-        <v>7114590</v>
+        <v>7114545</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,10 +8523,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141672</v>
+        <v>120141699</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8529,21 +8539,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8553,10 +8563,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506895</v>
+        <v>506982</v>
       </c>
       <c r="R72" t="n">
-        <v>7115116</v>
+        <v>7114588</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8589,11 +8599,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8620,10 +8625,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141675</v>
+        <v>120141697</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8636,21 +8641,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8660,10 +8665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506831</v>
+        <v>506874</v>
       </c>
       <c r="R73" t="n">
-        <v>7115012</v>
+        <v>7114372</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8696,11 +8701,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8727,10 +8727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141691</v>
+        <v>120141668</v>
       </c>
       <c r="B74" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8743,21 +8743,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8767,10 +8767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506952</v>
+        <v>506672</v>
       </c>
       <c r="R74" t="n">
-        <v>7114997</v>
+        <v>7114574</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8829,10 +8829,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141686</v>
+        <v>120141689</v>
       </c>
       <c r="B75" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8845,21 +8845,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506978</v>
+        <v>506964</v>
       </c>
       <c r="R75" t="n">
-        <v>7114547</v>
+        <v>7114937</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8931,10 +8931,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141692</v>
+        <v>120141681</v>
       </c>
       <c r="B76" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8947,21 +8947,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8971,10 +8971,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506954</v>
+        <v>506679</v>
       </c>
       <c r="R76" t="n">
-        <v>7115013</v>
+        <v>7114465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9007,6 +9007,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9033,7 +9038,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141694</v>
+        <v>120141688</v>
       </c>
       <c r="B77" t="n">
         <v>79623</v>
@@ -9073,10 +9078,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506824</v>
+        <v>506908</v>
       </c>
       <c r="R77" t="n">
-        <v>7114993</v>
+        <v>7114647</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9135,10 +9140,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141674</v>
+        <v>120141694</v>
       </c>
       <c r="B78" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9151,21 +9156,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9175,10 +9180,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506873</v>
+        <v>506824</v>
       </c>
       <c r="R78" t="n">
-        <v>7115121</v>
+        <v>7114993</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9211,11 +9216,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9242,10 +9242,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141696</v>
+        <v>120141677</v>
       </c>
       <c r="B79" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9258,21 +9258,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9282,10 +9282,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506756</v>
+        <v>506807</v>
       </c>
       <c r="R79" t="n">
-        <v>7114454</v>
+        <v>7114959</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9318,6 +9318,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9344,10 +9349,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141690</v>
+        <v>120141687</v>
       </c>
       <c r="B80" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9360,21 +9365,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9384,10 +9389,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506952</v>
+        <v>506979</v>
       </c>
       <c r="R80" t="n">
-        <v>7114935</v>
+        <v>7114590</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9446,10 +9451,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141707</v>
+        <v>120141684</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9462,21 +9467,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9486,10 +9491,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506822</v>
+        <v>507001</v>
       </c>
       <c r="R81" t="n">
-        <v>7114452</v>
+        <v>7114716</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9522,6 +9527,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9548,10 +9558,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141678</v>
+        <v>120141701</v>
       </c>
       <c r="B82" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9564,21 +9574,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9588,10 +9598,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506702</v>
+        <v>506918</v>
       </c>
       <c r="R82" t="n">
-        <v>7114515</v>
+        <v>7114686</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9624,11 +9634,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9655,7 +9660,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141698</v>
+        <v>120141695</v>
       </c>
       <c r="B83" t="n">
         <v>79623</v>
@@ -9695,10 +9700,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506955</v>
+        <v>506750</v>
       </c>
       <c r="R83" t="n">
-        <v>7114545</v>
+        <v>7114935</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9757,10 +9762,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141709</v>
+        <v>120141686</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9773,21 +9778,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9797,10 +9802,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506840</v>
+        <v>506978</v>
       </c>
       <c r="R84" t="n">
-        <v>7114370</v>
+        <v>7114547</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9859,10 +9864,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141697</v>
+        <v>120141704</v>
       </c>
       <c r="B85" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9875,21 +9880,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9899,10 +9904,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506874</v>
+        <v>506731</v>
       </c>
       <c r="R85" t="n">
-        <v>7114372</v>
+        <v>7114940</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9961,10 +9966,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141695</v>
+        <v>120141680</v>
       </c>
       <c r="B86" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9977,21 +9982,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10001,10 +10006,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506750</v>
+        <v>506703</v>
       </c>
       <c r="R86" t="n">
-        <v>7114935</v>
+        <v>7114470</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10037,6 +10042,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10063,10 +10073,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141682</v>
+        <v>120141667</v>
       </c>
       <c r="B87" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10079,21 +10089,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10103,10 +10113,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506688</v>
+        <v>506748</v>
       </c>
       <c r="R87" t="n">
-        <v>7114542</v>
+        <v>7114878</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10139,11 +10149,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10170,7 +10175,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141680</v>
+        <v>120141672</v>
       </c>
       <c r="B88" t="n">
         <v>57320</v>
@@ -10210,10 +10215,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506703</v>
+        <v>506895</v>
       </c>
       <c r="R88" t="n">
-        <v>7114470</v>
+        <v>7115116</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10250,7 +10255,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10277,10 +10282,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141677</v>
+        <v>120141696</v>
       </c>
       <c r="B89" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10293,21 +10298,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10317,10 +10322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506807</v>
+        <v>506756</v>
       </c>
       <c r="R89" t="n">
-        <v>7114959</v>
+        <v>7114454</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10353,11 +10358,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141700</v>
+        <v>120141673</v>
       </c>
       <c r="B51" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6342,20 +6342,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6363,33 +6363,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507032</v>
+        <v>506865</v>
       </c>
       <c r="R51" t="n">
-        <v>7114708</v>
+        <v>7115101</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6422,6 +6406,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6448,7 +6437,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141690</v>
+        <v>120141695</v>
       </c>
       <c r="B52" t="n">
         <v>79623</v>
@@ -6488,7 +6477,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506952</v>
+        <v>506750</v>
       </c>
       <c r="R52" t="n">
         <v>7114935</v>
@@ -6550,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141710</v>
+        <v>120141678</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6566,21 +6555,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6590,10 +6579,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506986</v>
+        <v>506702</v>
       </c>
       <c r="R53" t="n">
-        <v>7114613</v>
+        <v>7114515</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6626,6 +6615,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6652,10 +6646,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141706</v>
+        <v>120141687</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6668,21 +6662,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6692,10 +6686,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506637</v>
+        <v>506979</v>
       </c>
       <c r="R54" t="n">
-        <v>7114645</v>
+        <v>7114590</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6754,10 +6748,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141707</v>
+        <v>120141691</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6770,21 +6764,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6794,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506822</v>
+        <v>506952</v>
       </c>
       <c r="R55" t="n">
-        <v>7114452</v>
+        <v>7114997</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6856,10 +6850,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141666</v>
+        <v>120141674</v>
       </c>
       <c r="B56" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6872,21 +6866,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6896,10 +6890,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506960</v>
+        <v>506873</v>
       </c>
       <c r="R56" t="n">
-        <v>7115050</v>
+        <v>7115121</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6932,6 +6926,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6958,10 +6957,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141671</v>
+        <v>120141702</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6974,21 +6973,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6998,10 +6997,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507102</v>
+        <v>506729</v>
       </c>
       <c r="R57" t="n">
-        <v>7114733</v>
+        <v>7114816</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7034,11 +7033,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7065,10 +7059,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141692</v>
+        <v>120141707</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7081,21 +7075,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7105,10 +7099,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506954</v>
+        <v>506822</v>
       </c>
       <c r="R58" t="n">
-        <v>7115013</v>
+        <v>7114452</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7167,10 +7161,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141709</v>
+        <v>120141672</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7183,21 +7177,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7207,10 +7201,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506840</v>
+        <v>506895</v>
       </c>
       <c r="R59" t="n">
-        <v>7114370</v>
+        <v>7115116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7243,6 +7237,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7269,10 +7268,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141683</v>
+        <v>120141703</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7285,21 +7284,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7309,10 +7308,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507001</v>
+        <v>506664</v>
       </c>
       <c r="R60" t="n">
-        <v>7114608</v>
+        <v>7114490</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7345,11 +7344,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7376,10 +7370,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141682</v>
+        <v>120141705</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7392,21 +7386,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7416,10 +7410,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506688</v>
+        <v>506714</v>
       </c>
       <c r="R61" t="n">
-        <v>7114542</v>
+        <v>7114740</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7452,11 +7446,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7483,10 +7472,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141674</v>
+        <v>120141690</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7499,21 +7488,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7523,10 +7512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506873</v>
+        <v>506952</v>
       </c>
       <c r="R62" t="n">
-        <v>7115121</v>
+        <v>7114935</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7559,11 +7548,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7590,10 +7574,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141675</v>
+        <v>120141667</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7606,21 +7590,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7630,10 +7614,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506831</v>
+        <v>506748</v>
       </c>
       <c r="R63" t="n">
-        <v>7115012</v>
+        <v>7114878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7666,11 +7650,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7697,10 +7676,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141703</v>
+        <v>120141686</v>
       </c>
       <c r="B64" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7692,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7716,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506664</v>
+        <v>506978</v>
       </c>
       <c r="R64" t="n">
-        <v>7114490</v>
+        <v>7114547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7778,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141691</v>
+        <v>120141675</v>
       </c>
       <c r="B65" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7794,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7818,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506952</v>
+        <v>506831</v>
       </c>
       <c r="R65" t="n">
-        <v>7114997</v>
+        <v>7115012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7875,6 +7854,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7901,10 +7885,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141673</v>
+        <v>120141699</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7917,21 +7901,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7941,10 +7925,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506865</v>
+        <v>506982</v>
       </c>
       <c r="R66" t="n">
-        <v>7115101</v>
+        <v>7114588</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7977,11 +7961,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8008,10 +7987,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141678</v>
+        <v>120141700</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8020,20 +7999,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8041,17 +8020,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506702</v>
+        <v>507032</v>
       </c>
       <c r="R67" t="n">
-        <v>7114515</v>
+        <v>7114708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8084,11 +8079,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8115,7 +8105,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141698</v>
+        <v>120141689</v>
       </c>
       <c r="B68" t="n">
         <v>79623</v>
@@ -8155,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506955</v>
+        <v>506964</v>
       </c>
       <c r="R68" t="n">
-        <v>7114545</v>
+        <v>7114937</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8217,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141705</v>
+        <v>120141697</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8233,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8257,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506714</v>
+        <v>506874</v>
       </c>
       <c r="R69" t="n">
-        <v>7114740</v>
+        <v>7114372</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8319,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141702</v>
+        <v>120141680</v>
       </c>
       <c r="B70" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8335,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8359,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506729</v>
+        <v>506703</v>
       </c>
       <c r="R70" t="n">
-        <v>7114816</v>
+        <v>7114470</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8395,6 +8385,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8421,10 +8416,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141685</v>
+        <v>120141704</v>
       </c>
       <c r="B71" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8437,21 +8432,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8461,10 +8456,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506955</v>
+        <v>506731</v>
       </c>
       <c r="R71" t="n">
-        <v>7114545</v>
+        <v>7114940</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8523,7 +8518,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141699</v>
+        <v>120141692</v>
       </c>
       <c r="B72" t="n">
         <v>79623</v>
@@ -8563,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506982</v>
+        <v>506954</v>
       </c>
       <c r="R72" t="n">
-        <v>7114588</v>
+        <v>7115013</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8625,10 +8620,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141697</v>
+        <v>120141710</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8641,21 +8636,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8665,10 +8660,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506874</v>
+        <v>506986</v>
       </c>
       <c r="R73" t="n">
-        <v>7114372</v>
+        <v>7114613</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8727,10 +8722,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141668</v>
+        <v>120141671</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8743,21 +8738,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8767,10 +8762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506672</v>
+        <v>507102</v>
       </c>
       <c r="R74" t="n">
-        <v>7114574</v>
+        <v>7114733</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8803,6 +8798,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8829,10 +8829,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141689</v>
+        <v>120141681</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8845,21 +8845,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506964</v>
+        <v>506679</v>
       </c>
       <c r="R75" t="n">
-        <v>7114937</v>
+        <v>7114465</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8905,6 +8905,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8931,7 +8936,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141681</v>
+        <v>120141683</v>
       </c>
       <c r="B76" t="n">
         <v>57320</v>
@@ -8971,10 +8976,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506679</v>
+        <v>507001</v>
       </c>
       <c r="R76" t="n">
-        <v>7114465</v>
+        <v>7114608</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9011,7 +9016,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9038,7 +9043,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141688</v>
+        <v>120141696</v>
       </c>
       <c r="B77" t="n">
         <v>79623</v>
@@ -9078,10 +9083,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506908</v>
+        <v>506756</v>
       </c>
       <c r="R77" t="n">
-        <v>7114647</v>
+        <v>7114454</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9140,10 +9145,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141694</v>
+        <v>120141684</v>
       </c>
       <c r="B78" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9156,21 +9161,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9180,10 +9185,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506824</v>
+        <v>507001</v>
       </c>
       <c r="R78" t="n">
-        <v>7114993</v>
+        <v>7114716</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9216,6 +9221,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9242,10 +9252,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141677</v>
+        <v>120141701</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9258,21 +9268,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9282,10 +9292,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506807</v>
+        <v>506918</v>
       </c>
       <c r="R79" t="n">
-        <v>7114959</v>
+        <v>7114686</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9318,11 +9328,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9349,10 +9354,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141687</v>
+        <v>120141694</v>
       </c>
       <c r="B80" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9365,21 +9370,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9389,10 +9394,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506979</v>
+        <v>506824</v>
       </c>
       <c r="R80" t="n">
-        <v>7114590</v>
+        <v>7114993</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9451,7 +9456,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141684</v>
+        <v>120141682</v>
       </c>
       <c r="B81" t="n">
         <v>57320</v>
@@ -9491,10 +9496,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507001</v>
+        <v>506688</v>
       </c>
       <c r="R81" t="n">
-        <v>7114716</v>
+        <v>7114542</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9531,7 +9536,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9558,10 +9563,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141701</v>
+        <v>120141706</v>
       </c>
       <c r="B82" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9574,21 +9579,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9598,10 +9603,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506918</v>
+        <v>506637</v>
       </c>
       <c r="R82" t="n">
-        <v>7114686</v>
+        <v>7114645</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9660,7 +9665,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141695</v>
+        <v>120141698</v>
       </c>
       <c r="B83" t="n">
         <v>79623</v>
@@ -9700,10 +9705,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506750</v>
+        <v>506955</v>
       </c>
       <c r="R83" t="n">
-        <v>7114935</v>
+        <v>7114545</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9762,10 +9767,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141686</v>
+        <v>120141709</v>
       </c>
       <c r="B84" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9778,21 +9783,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9802,10 +9807,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506978</v>
+        <v>506840</v>
       </c>
       <c r="R84" t="n">
-        <v>7114547</v>
+        <v>7114370</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9864,10 +9869,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141704</v>
+        <v>120141677</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9880,21 +9885,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9904,10 +9909,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506731</v>
+        <v>506807</v>
       </c>
       <c r="R85" t="n">
-        <v>7114940</v>
+        <v>7114959</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9940,6 +9945,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9966,10 +9976,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141680</v>
+        <v>120141685</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9982,21 +9992,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10006,10 +10016,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506703</v>
+        <v>506955</v>
       </c>
       <c r="R86" t="n">
-        <v>7114470</v>
+        <v>7114545</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10042,11 +10052,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10073,7 +10078,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141667</v>
+        <v>120141668</v>
       </c>
       <c r="B87" t="n">
         <v>90580</v>
@@ -10113,10 +10118,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506748</v>
+        <v>506672</v>
       </c>
       <c r="R87" t="n">
-        <v>7114878</v>
+        <v>7114574</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10175,10 +10180,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141672</v>
+        <v>120141666</v>
       </c>
       <c r="B88" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10191,21 +10196,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10215,10 +10220,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506895</v>
+        <v>506960</v>
       </c>
       <c r="R88" t="n">
-        <v>7115116</v>
+        <v>7115050</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10251,11 +10256,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10282,7 +10282,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141696</v>
+        <v>120141688</v>
       </c>
       <c r="B89" t="n">
         <v>79623</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506756</v>
+        <v>506908</v>
       </c>
       <c r="R89" t="n">
-        <v>7114454</v>
+        <v>7114647</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6437,10 +6437,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141695</v>
+        <v>120141687</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6453,21 +6453,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506750</v>
+        <v>506979</v>
       </c>
       <c r="R52" t="n">
-        <v>7114935</v>
+        <v>7114590</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141678</v>
+        <v>120141695</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506702</v>
+        <v>506750</v>
       </c>
       <c r="R53" t="n">
-        <v>7114515</v>
+        <v>7114935</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6615,11 +6615,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6646,10 +6641,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141687</v>
+        <v>120141678</v>
       </c>
       <c r="B54" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6662,21 +6657,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6686,10 +6681,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506979</v>
+        <v>506702</v>
       </c>
       <c r="R54" t="n">
-        <v>7114590</v>
+        <v>7114515</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6722,6 +6717,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7987,10 +7987,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141700</v>
+        <v>120141689</v>
       </c>
       <c r="B67" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7999,54 +7999,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507032</v>
+        <v>506964</v>
       </c>
       <c r="R67" t="n">
-        <v>7114708</v>
+        <v>7114937</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,7 +8089,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141689</v>
+        <v>120141697</v>
       </c>
       <c r="B68" t="n">
         <v>79623</v>
@@ -8145,10 +8129,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506964</v>
+        <v>506874</v>
       </c>
       <c r="R68" t="n">
-        <v>7114937</v>
+        <v>7114372</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8191,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141697</v>
+        <v>120141680</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8207,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8231,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506874</v>
+        <v>506703</v>
       </c>
       <c r="R69" t="n">
-        <v>7114372</v>
+        <v>7114470</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8283,6 +8267,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8309,10 +8298,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141680</v>
+        <v>120141700</v>
       </c>
       <c r="B70" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8321,20 +8310,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8342,17 +8331,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506703</v>
+        <v>507032</v>
       </c>
       <c r="R70" t="n">
-        <v>7114470</v>
+        <v>7114708</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8385,11 +8390,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8936,10 +8936,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141683</v>
+        <v>120141696</v>
       </c>
       <c r="B76" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507001</v>
+        <v>506756</v>
       </c>
       <c r="R76" t="n">
-        <v>7114608</v>
+        <v>7114454</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9012,11 +9012,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9043,10 +9038,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141696</v>
+        <v>120141683</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9054,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9083,10 +9078,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506756</v>
+        <v>507001</v>
       </c>
       <c r="R77" t="n">
-        <v>7114454</v>
+        <v>7114608</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,6 +9114,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9145,10 +9145,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141684</v>
+        <v>120141701</v>
       </c>
       <c r="B78" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9161,21 +9161,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9185,10 +9185,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507001</v>
+        <v>506918</v>
       </c>
       <c r="R78" t="n">
-        <v>7114716</v>
+        <v>7114686</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9221,11 +9221,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9252,10 +9247,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141701</v>
+        <v>120141684</v>
       </c>
       <c r="B79" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9268,21 +9263,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9292,10 +9287,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506918</v>
+        <v>507001</v>
       </c>
       <c r="R79" t="n">
-        <v>7114686</v>
+        <v>7114716</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9328,6 +9323,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9354,10 +9354,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141694</v>
+        <v>120141682</v>
       </c>
       <c r="B80" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9370,21 +9370,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506824</v>
+        <v>506688</v>
       </c>
       <c r="R80" t="n">
-        <v>7114993</v>
+        <v>7114542</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9430,6 +9430,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9456,10 +9461,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141682</v>
+        <v>120141694</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9472,21 +9477,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9496,10 +9501,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506688</v>
+        <v>506824</v>
       </c>
       <c r="R81" t="n">
-        <v>7114542</v>
+        <v>7114993</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9532,11 +9537,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,7 +6330,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141673</v>
+        <v>120141683</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506865</v>
+        <v>507001</v>
       </c>
       <c r="R51" t="n">
-        <v>7115101</v>
+        <v>7114608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6437,10 +6437,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141687</v>
+        <v>120141671</v>
       </c>
       <c r="B52" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6453,21 +6453,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506979</v>
+        <v>507102</v>
       </c>
       <c r="R52" t="n">
-        <v>7114590</v>
+        <v>7114733</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6513,6 +6513,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6539,10 +6544,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141695</v>
+        <v>120141705</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,21 +6560,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506750</v>
+        <v>506714</v>
       </c>
       <c r="R53" t="n">
-        <v>7114935</v>
+        <v>7114740</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6641,10 +6646,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141678</v>
+        <v>120141690</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6657,21 +6662,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6681,10 +6686,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506702</v>
+        <v>506952</v>
       </c>
       <c r="R54" t="n">
-        <v>7114515</v>
+        <v>7114935</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6717,11 +6722,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6748,7 +6748,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141691</v>
+        <v>120141694</v>
       </c>
       <c r="B55" t="n">
         <v>79623</v>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506952</v>
+        <v>506824</v>
       </c>
       <c r="R55" t="n">
-        <v>7114997</v>
+        <v>7114993</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6850,7 +6850,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141674</v>
+        <v>120141680</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506873</v>
+        <v>506703</v>
       </c>
       <c r="R56" t="n">
-        <v>7115121</v>
+        <v>7114470</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141702</v>
+        <v>120141703</v>
       </c>
       <c r="B57" t="n">
         <v>90598</v>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506729</v>
+        <v>506664</v>
       </c>
       <c r="R57" t="n">
-        <v>7114816</v>
+        <v>7114490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7059,10 +7059,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141707</v>
+        <v>120141691</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506822</v>
+        <v>506952</v>
       </c>
       <c r="R58" t="n">
-        <v>7114452</v>
+        <v>7114997</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141672</v>
+        <v>120141689</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506895</v>
+        <v>506964</v>
       </c>
       <c r="R59" t="n">
-        <v>7115116</v>
+        <v>7114937</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7237,11 +7237,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7268,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141703</v>
+        <v>120141687</v>
       </c>
       <c r="B60" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7284,21 +7279,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7308,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506664</v>
+        <v>506979</v>
       </c>
       <c r="R60" t="n">
-        <v>7114490</v>
+        <v>7114590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7370,10 +7365,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141705</v>
+        <v>120141666</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7386,21 +7381,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7410,10 +7405,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506714</v>
+        <v>506960</v>
       </c>
       <c r="R61" t="n">
-        <v>7114740</v>
+        <v>7115050</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7472,10 +7467,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141690</v>
+        <v>120141685</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7488,21 +7483,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7512,10 +7507,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506952</v>
+        <v>506955</v>
       </c>
       <c r="R62" t="n">
-        <v>7114935</v>
+        <v>7114545</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7574,10 +7569,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141667</v>
+        <v>120141682</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7590,21 +7585,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7614,10 +7609,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506748</v>
+        <v>506688</v>
       </c>
       <c r="R63" t="n">
-        <v>7114878</v>
+        <v>7114542</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7650,6 +7645,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7676,10 +7676,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141686</v>
+        <v>120141675</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7692,21 +7692,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7716,10 +7716,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506978</v>
+        <v>506831</v>
       </c>
       <c r="R64" t="n">
-        <v>7114547</v>
+        <v>7115012</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7752,6 +7752,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7778,10 +7783,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141675</v>
+        <v>120141696</v>
       </c>
       <c r="B65" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7794,21 +7799,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7818,10 +7823,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506831</v>
+        <v>506756</v>
       </c>
       <c r="R65" t="n">
-        <v>7115012</v>
+        <v>7114454</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7854,11 +7859,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7885,10 +7885,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141699</v>
+        <v>120141707</v>
       </c>
       <c r="B66" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7901,21 +7901,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506982</v>
+        <v>506822</v>
       </c>
       <c r="R66" t="n">
-        <v>7114588</v>
+        <v>7114452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141689</v>
+        <v>120141697</v>
       </c>
       <c r="B67" t="n">
         <v>79623</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506964</v>
+        <v>506874</v>
       </c>
       <c r="R67" t="n">
-        <v>7114937</v>
+        <v>7114372</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8089,10 +8089,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120141697</v>
+        <v>120141701</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8105,21 +8105,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506874</v>
+        <v>506918</v>
       </c>
       <c r="R68" t="n">
-        <v>7114372</v>
+        <v>7114686</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8191,7 +8191,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141680</v>
+        <v>120141677</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506703</v>
+        <v>506807</v>
       </c>
       <c r="R69" t="n">
-        <v>7114470</v>
+        <v>7114959</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141700</v>
+        <v>120141706</v>
       </c>
       <c r="B70" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8310,54 +8310,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507032</v>
+        <v>506637</v>
       </c>
       <c r="R70" t="n">
-        <v>7114708</v>
+        <v>7114645</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8416,10 +8400,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141704</v>
+        <v>120141695</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8432,21 +8416,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8456,10 +8440,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506731</v>
+        <v>506750</v>
       </c>
       <c r="R71" t="n">
-        <v>7114940</v>
+        <v>7114935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8518,10 +8502,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141692</v>
+        <v>120141686</v>
       </c>
       <c r="B72" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,21 +8518,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8558,10 +8542,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506954</v>
+        <v>506978</v>
       </c>
       <c r="R72" t="n">
-        <v>7115013</v>
+        <v>7114547</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8620,10 +8604,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141710</v>
+        <v>120141668</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8636,21 +8620,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8660,10 +8644,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506986</v>
+        <v>506672</v>
       </c>
       <c r="R73" t="n">
-        <v>7114613</v>
+        <v>7114574</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8722,10 +8706,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141671</v>
+        <v>120141698</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8738,21 +8722,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8762,10 +8746,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507102</v>
+        <v>506955</v>
       </c>
       <c r="R74" t="n">
-        <v>7114733</v>
+        <v>7114545</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8798,11 +8782,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8829,10 +8808,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141681</v>
+        <v>120141699</v>
       </c>
       <c r="B75" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8845,21 +8824,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8869,10 +8848,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506679</v>
+        <v>506982</v>
       </c>
       <c r="R75" t="n">
-        <v>7114465</v>
+        <v>7114588</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8905,11 +8884,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8936,7 +8910,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141696</v>
+        <v>120141688</v>
       </c>
       <c r="B76" t="n">
         <v>79623</v>
@@ -8976,10 +8950,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506756</v>
+        <v>506908</v>
       </c>
       <c r="R76" t="n">
-        <v>7114454</v>
+        <v>7114647</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9038,10 +9012,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141683</v>
+        <v>120141702</v>
       </c>
       <c r="B77" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9054,21 +9028,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9078,10 +9052,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507001</v>
+        <v>506729</v>
       </c>
       <c r="R77" t="n">
-        <v>7114608</v>
+        <v>7114816</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9114,11 +9088,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9145,10 +9114,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141701</v>
+        <v>120141700</v>
       </c>
       <c r="B78" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9157,38 +9126,54 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506918</v>
+        <v>507032</v>
       </c>
       <c r="R78" t="n">
-        <v>7114686</v>
+        <v>7114708</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9247,7 +9232,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141684</v>
+        <v>120141678</v>
       </c>
       <c r="B79" t="n">
         <v>57320</v>
@@ -9287,10 +9272,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507001</v>
+        <v>506702</v>
       </c>
       <c r="R79" t="n">
-        <v>7114716</v>
+        <v>7114515</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9327,7 +9312,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9354,10 +9339,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141682</v>
+        <v>120141710</v>
       </c>
       <c r="B80" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9370,21 +9355,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9394,10 +9379,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506688</v>
+        <v>506986</v>
       </c>
       <c r="R80" t="n">
-        <v>7114542</v>
+        <v>7114613</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9430,11 +9415,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9461,7 +9441,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141694</v>
+        <v>120141692</v>
       </c>
       <c r="B81" t="n">
         <v>79623</v>
@@ -9501,10 +9481,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506824</v>
+        <v>506954</v>
       </c>
       <c r="R81" t="n">
-        <v>7114993</v>
+        <v>7115013</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9563,7 +9543,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141706</v>
+        <v>120141704</v>
       </c>
       <c r="B82" t="n">
         <v>78542</v>
@@ -9603,10 +9583,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506637</v>
+        <v>506731</v>
       </c>
       <c r="R82" t="n">
-        <v>7114645</v>
+        <v>7114940</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9665,10 +9645,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141698</v>
+        <v>120141667</v>
       </c>
       <c r="B83" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9681,21 +9661,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9705,10 +9685,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506955</v>
+        <v>506748</v>
       </c>
       <c r="R83" t="n">
-        <v>7114545</v>
+        <v>7114878</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9767,10 +9747,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141709</v>
+        <v>120141672</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9783,21 +9763,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9807,10 +9787,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506840</v>
+        <v>506895</v>
       </c>
       <c r="R84" t="n">
-        <v>7114370</v>
+        <v>7115116</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9843,6 +9823,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9869,10 +9854,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141677</v>
+        <v>120141709</v>
       </c>
       <c r="B85" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9885,21 +9870,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9909,10 +9894,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506807</v>
+        <v>506840</v>
       </c>
       <c r="R85" t="n">
-        <v>7114959</v>
+        <v>7114370</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9945,11 +9930,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9976,10 +9956,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141685</v>
+        <v>120141673</v>
       </c>
       <c r="B86" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9992,21 +9972,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10016,10 +9996,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506955</v>
+        <v>506865</v>
       </c>
       <c r="R86" t="n">
-        <v>7114545</v>
+        <v>7115101</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10052,6 +10032,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10078,10 +10063,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141668</v>
+        <v>120141681</v>
       </c>
       <c r="B87" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10094,21 +10079,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10118,10 +10103,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506672</v>
+        <v>506679</v>
       </c>
       <c r="R87" t="n">
-        <v>7114574</v>
+        <v>7114465</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10154,6 +10139,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10180,10 +10170,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141666</v>
+        <v>120141674</v>
       </c>
       <c r="B88" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10196,21 +10186,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10220,10 +10210,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506960</v>
+        <v>506873</v>
       </c>
       <c r="R88" t="n">
-        <v>7115050</v>
+        <v>7115121</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10256,6 +10246,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10282,10 +10277,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141688</v>
+        <v>120141684</v>
       </c>
       <c r="B89" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10298,21 +10293,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10322,10 +10317,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506908</v>
+        <v>507001</v>
       </c>
       <c r="R89" t="n">
-        <v>7114647</v>
+        <v>7114716</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10358,6 +10353,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6330,10 +6330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141683</v>
+        <v>120141691</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507001</v>
+        <v>506952</v>
       </c>
       <c r="R51" t="n">
-        <v>7114608</v>
+        <v>7114997</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6406,11 +6406,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6437,10 +6432,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141671</v>
+        <v>120141695</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6453,21 +6448,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507102</v>
+        <v>506750</v>
       </c>
       <c r="R52" t="n">
-        <v>7114733</v>
+        <v>7114935</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6513,11 +6508,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6544,10 +6534,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141705</v>
+        <v>120141692</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6560,21 +6550,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6584,10 +6574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506714</v>
+        <v>506954</v>
       </c>
       <c r="R53" t="n">
-        <v>7114740</v>
+        <v>7115013</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6646,7 +6636,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141690</v>
+        <v>120141697</v>
       </c>
       <c r="B54" t="n">
         <v>79623</v>
@@ -6686,10 +6676,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506952</v>
+        <v>506874</v>
       </c>
       <c r="R54" t="n">
-        <v>7114935</v>
+        <v>7114372</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6748,10 +6738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141694</v>
+        <v>120141668</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6764,21 +6754,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6778,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506824</v>
+        <v>506672</v>
       </c>
       <c r="R55" t="n">
-        <v>7114993</v>
+        <v>7114574</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6850,7 +6840,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141680</v>
+        <v>120141672</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6890,10 +6880,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506703</v>
+        <v>506895</v>
       </c>
       <c r="R56" t="n">
-        <v>7114470</v>
+        <v>7115116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6930,7 +6920,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6957,10 +6947,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141703</v>
+        <v>120141674</v>
       </c>
       <c r="B57" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6973,21 +6963,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506664</v>
+        <v>506873</v>
       </c>
       <c r="R57" t="n">
-        <v>7114490</v>
+        <v>7115121</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7033,6 +7023,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7059,10 +7054,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120141691</v>
+        <v>120141706</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7075,21 +7070,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7099,10 +7094,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506952</v>
+        <v>506637</v>
       </c>
       <c r="R58" t="n">
-        <v>7114997</v>
+        <v>7114645</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7161,10 +7156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120141689</v>
+        <v>120141684</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7177,21 +7172,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7201,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506964</v>
+        <v>507001</v>
       </c>
       <c r="R59" t="n">
-        <v>7114937</v>
+        <v>7114716</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7237,6 +7232,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141687</v>
+        <v>120141700</v>
       </c>
       <c r="B60" t="n">
-        <v>79624</v>
+        <v>57431</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7275,38 +7275,54 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506979</v>
+        <v>507032</v>
       </c>
       <c r="R60" t="n">
-        <v>7114590</v>
+        <v>7114708</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7365,10 +7381,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120141666</v>
+        <v>120141699</v>
       </c>
       <c r="B61" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7381,21 +7397,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7405,10 +7421,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506960</v>
+        <v>506982</v>
       </c>
       <c r="R61" t="n">
-        <v>7115050</v>
+        <v>7114588</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7467,10 +7483,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141685</v>
+        <v>120141703</v>
       </c>
       <c r="B62" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,21 +7499,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7507,10 +7523,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506955</v>
+        <v>506664</v>
       </c>
       <c r="R62" t="n">
-        <v>7114545</v>
+        <v>7114490</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7569,10 +7585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120141682</v>
+        <v>120141709</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7585,21 +7601,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7609,10 +7625,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506688</v>
+        <v>506840</v>
       </c>
       <c r="R63" t="n">
-        <v>7114542</v>
+        <v>7114370</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7645,11 +7661,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7676,10 +7687,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120141675</v>
+        <v>120141698</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7692,21 +7703,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7716,10 +7727,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506831</v>
+        <v>506955</v>
       </c>
       <c r="R64" t="n">
-        <v>7115012</v>
+        <v>7114545</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7752,11 +7763,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7783,7 +7789,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120141696</v>
+        <v>120141694</v>
       </c>
       <c r="B65" t="n">
         <v>79623</v>
@@ -7823,10 +7829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506756</v>
+        <v>506824</v>
       </c>
       <c r="R65" t="n">
-        <v>7114454</v>
+        <v>7114993</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7885,10 +7891,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120141707</v>
+        <v>120141696</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7901,21 +7907,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7925,10 +7931,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506822</v>
+        <v>506756</v>
       </c>
       <c r="R66" t="n">
-        <v>7114452</v>
+        <v>7114454</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7987,10 +7993,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120141697</v>
+        <v>120141680</v>
       </c>
       <c r="B67" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8003,21 +8009,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8027,10 +8033,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506874</v>
+        <v>506703</v>
       </c>
       <c r="R67" t="n">
-        <v>7114372</v>
+        <v>7114470</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8063,6 +8069,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8191,7 +8202,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120141677</v>
+        <v>120141678</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -8231,10 +8242,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506807</v>
+        <v>506702</v>
       </c>
       <c r="R69" t="n">
-        <v>7114959</v>
+        <v>7114515</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8298,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120141706</v>
+        <v>120141686</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8314,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8338,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506637</v>
+        <v>506978</v>
       </c>
       <c r="R70" t="n">
-        <v>7114645</v>
+        <v>7114547</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8400,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120141695</v>
+        <v>120141667</v>
       </c>
       <c r="B71" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8416,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8440,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506750</v>
+        <v>506748</v>
       </c>
       <c r="R71" t="n">
-        <v>7114935</v>
+        <v>7114878</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8513,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120141686</v>
+        <v>120141685</v>
       </c>
       <c r="B72" t="n">
         <v>79624</v>
@@ -8542,10 +8553,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506978</v>
+        <v>506955</v>
       </c>
       <c r="R72" t="n">
-        <v>7114547</v>
+        <v>7114545</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8604,10 +8615,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120141668</v>
+        <v>120141707</v>
       </c>
       <c r="B73" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8620,21 +8631,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8644,10 +8655,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506672</v>
+        <v>506822</v>
       </c>
       <c r="R73" t="n">
-        <v>7114574</v>
+        <v>7114452</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8706,10 +8717,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120141698</v>
+        <v>120141677</v>
       </c>
       <c r="B74" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8722,21 +8733,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8746,10 +8757,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506955</v>
+        <v>506807</v>
       </c>
       <c r="R74" t="n">
-        <v>7114545</v>
+        <v>7114959</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8782,6 +8793,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8808,7 +8824,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120141699</v>
+        <v>120141689</v>
       </c>
       <c r="B75" t="n">
         <v>79623</v>
@@ -8848,10 +8864,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506982</v>
+        <v>506964</v>
       </c>
       <c r="R75" t="n">
-        <v>7114588</v>
+        <v>7114937</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8910,10 +8926,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120141688</v>
+        <v>120141682</v>
       </c>
       <c r="B76" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8926,21 +8942,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8950,10 +8966,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506908</v>
+        <v>506688</v>
       </c>
       <c r="R76" t="n">
-        <v>7114647</v>
+        <v>7114542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8986,6 +9002,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9012,10 +9033,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120141702</v>
+        <v>120141687</v>
       </c>
       <c r="B77" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9028,21 +9049,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9052,10 +9073,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506729</v>
+        <v>506979</v>
       </c>
       <c r="R77" t="n">
-        <v>7114816</v>
+        <v>7114590</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9114,10 +9135,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120141700</v>
+        <v>120141704</v>
       </c>
       <c r="B78" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9126,54 +9147,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507032</v>
+        <v>506731</v>
       </c>
       <c r="R78" t="n">
-        <v>7114708</v>
+        <v>7114940</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9232,10 +9237,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120141678</v>
+        <v>120141688</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9248,21 +9253,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9272,10 +9277,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506702</v>
+        <v>506908</v>
       </c>
       <c r="R79" t="n">
-        <v>7114515</v>
+        <v>7114647</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9308,11 +9313,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9339,10 +9339,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120141710</v>
+        <v>120141702</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9355,21 +9355,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506986</v>
+        <v>506729</v>
       </c>
       <c r="R80" t="n">
-        <v>7114613</v>
+        <v>7114816</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9441,10 +9441,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120141692</v>
+        <v>120141681</v>
       </c>
       <c r="B81" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9457,21 +9457,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506954</v>
+        <v>506679</v>
       </c>
       <c r="R81" t="n">
-        <v>7115013</v>
+        <v>7114465</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9517,6 +9517,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9543,7 +9548,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120141704</v>
+        <v>120141710</v>
       </c>
       <c r="B82" t="n">
         <v>78542</v>
@@ -9583,10 +9588,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506731</v>
+        <v>506986</v>
       </c>
       <c r="R82" t="n">
-        <v>7114940</v>
+        <v>7114613</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9645,10 +9650,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120141667</v>
+        <v>120141683</v>
       </c>
       <c r="B83" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9661,21 +9666,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9685,10 +9690,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506748</v>
+        <v>507001</v>
       </c>
       <c r="R83" t="n">
-        <v>7114878</v>
+        <v>7114608</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9721,6 +9726,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9747,7 +9757,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141672</v>
+        <v>120141675</v>
       </c>
       <c r="B84" t="n">
         <v>57320</v>
@@ -9787,10 +9797,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506895</v>
+        <v>506831</v>
       </c>
       <c r="R84" t="n">
-        <v>7115116</v>
+        <v>7115012</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9827,7 +9837,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9854,7 +9864,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141709</v>
+        <v>120141705</v>
       </c>
       <c r="B85" t="n">
         <v>78542</v>
@@ -9894,10 +9904,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506840</v>
+        <v>506714</v>
       </c>
       <c r="R85" t="n">
-        <v>7114370</v>
+        <v>7114740</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9956,10 +9966,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120141673</v>
+        <v>120141666</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9972,21 +9982,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9996,10 +10006,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506865</v>
+        <v>506960</v>
       </c>
       <c r="R86" t="n">
-        <v>7115101</v>
+        <v>7115050</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10032,11 +10042,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10063,7 +10068,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120141681</v>
+        <v>120141671</v>
       </c>
       <c r="B87" t="n">
         <v>57320</v>
@@ -10103,10 +10108,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506679</v>
+        <v>507102</v>
       </c>
       <c r="R87" t="n">
-        <v>7114465</v>
+        <v>7114733</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10143,7 +10148,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10170,7 +10175,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120141674</v>
+        <v>120141673</v>
       </c>
       <c r="B88" t="n">
         <v>57320</v>
@@ -10210,10 +10215,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506873</v>
+        <v>506865</v>
       </c>
       <c r="R88" t="n">
-        <v>7115121</v>
+        <v>7115101</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10250,7 +10255,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10277,10 +10282,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120141684</v>
+        <v>120141690</v>
       </c>
       <c r="B89" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10293,21 +10298,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10317,10 +10322,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507001</v>
+        <v>506952</v>
       </c>
       <c r="R89" t="n">
-        <v>7114716</v>
+        <v>7114935</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10353,11 +10358,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6534,7 +6534,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141692</v>
+        <v>120141697</v>
       </c>
       <c r="B53" t="n">
         <v>79623</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506954</v>
+        <v>506874</v>
       </c>
       <c r="R53" t="n">
-        <v>7115013</v>
+        <v>7114372</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141697</v>
+        <v>120141692</v>
       </c>
       <c r="B54" t="n">
         <v>79623</v>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506874</v>
+        <v>506954</v>
       </c>
       <c r="R54" t="n">
-        <v>7114372</v>
+        <v>7115013</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141668</v>
+        <v>120141672</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6754,21 +6754,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506672</v>
+        <v>506895</v>
       </c>
       <c r="R55" t="n">
-        <v>7114574</v>
+        <v>7115116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6814,6 +6814,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6840,7 +6845,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120141672</v>
+        <v>120141674</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6880,10 +6885,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506895</v>
+        <v>506873</v>
       </c>
       <c r="R56" t="n">
-        <v>7115116</v>
+        <v>7115121</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6920,7 +6925,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6947,10 +6952,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120141674</v>
+        <v>120141668</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6963,21 +6968,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6987,10 +6992,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506873</v>
+        <v>506672</v>
       </c>
       <c r="R57" t="n">
-        <v>7115121</v>
+        <v>7114574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7023,11 +7028,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120141700</v>
+        <v>120141703</v>
       </c>
       <c r="B60" t="n">
-        <v>57431</v>
+        <v>90598</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7275,54 +7275,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507032</v>
+        <v>506664</v>
       </c>
       <c r="R60" t="n">
-        <v>7114708</v>
+        <v>7114490</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7483,10 +7467,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120141703</v>
+        <v>120141700</v>
       </c>
       <c r="B62" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7495,38 +7479,54 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506664</v>
+        <v>507032</v>
       </c>
       <c r="R62" t="n">
-        <v>7114490</v>
+        <v>7114708</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9757,10 +9757,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120141675</v>
+        <v>120141705</v>
       </c>
       <c r="B84" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506831</v>
+        <v>506714</v>
       </c>
       <c r="R84" t="n">
-        <v>7115012</v>
+        <v>7114740</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9833,11 +9833,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9864,10 +9859,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120141705</v>
+        <v>120141675</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9880,21 +9875,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9904,10 +9899,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506714</v>
+        <v>506831</v>
       </c>
       <c r="R85" t="n">
-        <v>7114740</v>
+        <v>7115012</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9940,6 +9935,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6227,7 +6227,7 @@
         <v>118221367</v>
       </c>
       <c r="B50" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -6227,7 +6227,7 @@
         <v>118221367</v>
       </c>
       <c r="B50" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89595642</v>
+        <v>89595663</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506762.8763270681</v>
+        <v>507036.7971198635</v>
       </c>
       <c r="R4" t="n">
-        <v>7115326.878433471</v>
+        <v>7114731.081843849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89595602</v>
+        <v>89595669</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507135.1893000957</v>
+        <v>506897.8464952148</v>
       </c>
       <c r="R5" t="n">
-        <v>7114691.164315581</v>
+        <v>7114739.93209392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89595857</v>
+        <v>89595636</v>
       </c>
       <c r="B6" t="n">
-        <v>90074</v>
+        <v>78570</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507235.8505417521</v>
+        <v>506781.2047040357</v>
       </c>
       <c r="R6" t="n">
-        <v>7114803.098120484</v>
+        <v>7114936.016541568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89595663</v>
+        <v>89595633</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507036.7971198635</v>
+        <v>506793.1750779065</v>
       </c>
       <c r="R7" t="n">
-        <v>7114731.081843849</v>
+        <v>7114856.198487628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89595669</v>
+        <v>89595635</v>
       </c>
       <c r="B8" t="n">
         <v>78570</v>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506897.8464952148</v>
+        <v>506775.9538076027</v>
       </c>
       <c r="R8" t="n">
-        <v>7114739.93209392</v>
+        <v>7114939.931760079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89595830</v>
+        <v>89595618</v>
       </c>
       <c r="B9" t="n">
         <v>78570</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507242.8313918905</v>
+        <v>506819.1377885213</v>
       </c>
       <c r="R9" t="n">
-        <v>7114807.041330348</v>
+        <v>7114771.17331298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89595693</v>
+        <v>89595668</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
+        <v>78569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506734.1599884066</v>
+        <v>506781.0679131226</v>
       </c>
       <c r="R10" t="n">
-        <v>7115074.218504494</v>
+        <v>7114799.014384815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89595636</v>
+        <v>89595676</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506781.2047040357</v>
+        <v>506794.0382851731</v>
       </c>
       <c r="R11" t="n">
-        <v>7114936.016541568</v>
+        <v>7114860.9998238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89595633</v>
+        <v>89595655</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,21 +1851,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506793.1750779065</v>
+        <v>506819.1377885213</v>
       </c>
       <c r="R12" t="n">
-        <v>7114856.198487628</v>
+        <v>7114771.17331298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89595707</v>
+        <v>89595686</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507249.1121425516</v>
+        <v>506775.9538076027</v>
       </c>
       <c r="R13" t="n">
-        <v>7114736.807637845</v>
+        <v>7114939.931760079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89595804</v>
+        <v>89595641</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
+        <v>78569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,21 +2083,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507358.9857540908</v>
+        <v>506781.2047040357</v>
       </c>
       <c r="R14" t="n">
-        <v>7114278.886111268</v>
+        <v>7114936.016541568</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89595684</v>
+        <v>89595609</v>
       </c>
       <c r="B15" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506744.8171228337</v>
+        <v>506900.0289812936</v>
       </c>
       <c r="R15" t="n">
-        <v>7114994.837263474</v>
+        <v>7114740.809616276</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89595826</v>
+        <v>89595634</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507154.9798405373</v>
+        <v>506896.0610483468</v>
       </c>
       <c r="R16" t="n">
-        <v>7114823.853507597</v>
+        <v>7114756.94492677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89595698</v>
+        <v>120141667</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,34 +2431,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506752.0075831443</v>
+        <v>506748</v>
       </c>
       <c r="R17" t="n">
-        <v>7115103.051896133</v>
+        <v>7114878</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,22 +2485,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,26 +2505,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89595599</v>
+        <v>120141710</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,34 +2533,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507246.9174963917</v>
+        <v>506986</v>
       </c>
       <c r="R18" t="n">
-        <v>7114741.165800621</v>
+        <v>7114613</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,22 +2587,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,26 +2607,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89595643</v>
+        <v>120141681</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2663,34 +2635,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506728.1333730395</v>
+        <v>506679</v>
       </c>
       <c r="R19" t="n">
-        <v>7115033.194569207</v>
+        <v>7114465</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,22 +2689,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,26 +2714,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89595626</v>
+        <v>120141674</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2779,34 +2742,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507246.8010697782</v>
+        <v>506873</v>
       </c>
       <c r="R20" t="n">
-        <v>7114790.906719869</v>
+        <v>7115121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,22 +2796,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,26 +2821,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89595829</v>
+        <v>120141698</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,14 +2869,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507154.9798405373</v>
+        <v>506955</v>
       </c>
       <c r="R21" t="n">
-        <v>7114823.853507597</v>
+        <v>7114545</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2949,22 +2903,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,26 +2923,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89595678</v>
+        <v>120141686</v>
       </c>
       <c r="B22" t="n">
-        <v>78570</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,14 +2971,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506748.0760687894</v>
+        <v>506978</v>
       </c>
       <c r="R22" t="n">
-        <v>7115103.043323518</v>
+        <v>7114547</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3065,22 +3005,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,26 +3025,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89595649</v>
+        <v>120141673</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,34 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506744.8171228337</v>
+        <v>506865</v>
       </c>
       <c r="R23" t="n">
-        <v>7114994.837263474</v>
+        <v>7115101</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,22 +3107,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,26 +3132,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89595697</v>
+        <v>120141704</v>
       </c>
       <c r="B24" t="n">
-        <v>78570</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,34 +3160,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506737.2121644589</v>
+        <v>506731</v>
       </c>
       <c r="R24" t="n">
-        <v>7115076.842839749</v>
+        <v>7114940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3297,22 +3214,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,26 +3234,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89595861</v>
+        <v>120141685</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3359,34 +3262,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507221.9591160177</v>
+        <v>506955</v>
       </c>
       <c r="R25" t="n">
-        <v>7114203.066301864</v>
+        <v>7114545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,22 +3316,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,26 +3336,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89595828</v>
+        <v>120141666</v>
       </c>
       <c r="B26" t="n">
-        <v>78603</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3471,38 +3360,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507154.9798405373</v>
+        <v>506960</v>
       </c>
       <c r="R26" t="n">
-        <v>7114823.853507597</v>
+        <v>7115050</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3529,22 +3418,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,26 +3438,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89595835</v>
+        <v>120141709</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3611,14 +3486,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507160.9759869859</v>
+        <v>506840</v>
       </c>
       <c r="R27" t="n">
-        <v>7114875.788784604</v>
+        <v>7114370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,22 +3520,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,26 +3540,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89595801</v>
+        <v>120141690</v>
       </c>
       <c r="B28" t="n">
-        <v>78569</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3727,14 +3588,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507242.8313918905</v>
+        <v>506952</v>
       </c>
       <c r="R28" t="n">
-        <v>7114807.041330348</v>
+        <v>7114935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,22 +3622,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3791,26 +3642,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89595635</v>
+        <v>120141699</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3823,34 +3670,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506775.9538076027</v>
+        <v>506982</v>
       </c>
       <c r="R29" t="n">
-        <v>7114939.931760079</v>
+        <v>7114588</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3877,22 +3724,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,26 +3744,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89595659</v>
+        <v>120141680</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3939,34 +3772,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506774.8141906207</v>
+        <v>506703</v>
       </c>
       <c r="R30" t="n">
-        <v>7115261.030532516</v>
+        <v>7114470</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3993,22 +3826,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4023,26 +3851,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89595618</v>
+        <v>120141689</v>
       </c>
       <c r="B31" t="n">
-        <v>78570</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4055,34 +3879,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506819.1377885213</v>
+        <v>506964</v>
       </c>
       <c r="R31" t="n">
-        <v>7114771.17331298</v>
+        <v>7114937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4109,22 +3933,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4139,26 +3953,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89595706</v>
+        <v>120141688</v>
       </c>
       <c r="B32" t="n">
-        <v>78569</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4191,14 +4001,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506728.1333730395</v>
+        <v>506908</v>
       </c>
       <c r="R32" t="n">
-        <v>7115033.194569207</v>
+        <v>7114647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4225,22 +4035,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,26 +4055,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89595809</v>
+        <v>120141687</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
+        <v>79624</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4287,34 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507240.0854408693</v>
+        <v>506979</v>
       </c>
       <c r="R33" t="n">
-        <v>7113925.978852787</v>
+        <v>7114590</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4341,22 +4137,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4371,26 +4157,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89595647</v>
+        <v>120141677</v>
       </c>
       <c r="B34" t="n">
-        <v>78596</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4399,38 +4181,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507143.0241826411</v>
+        <v>506807</v>
       </c>
       <c r="R34" t="n">
-        <v>7114703.836119371</v>
+        <v>7114959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4457,22 +4239,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4487,26 +4264,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>89595668</v>
+        <v>120141705</v>
       </c>
       <c r="B35" t="n">
-        <v>78569</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4519,34 +4292,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506781.0679131226</v>
+        <v>506714</v>
       </c>
       <c r="R35" t="n">
-        <v>7114799.014384815</v>
+        <v>7114740</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4573,22 +4346,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4603,26 +4366,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89595664</v>
+        <v>120141678</v>
       </c>
       <c r="B36" t="n">
-        <v>77506</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4635,34 +4394,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507213.7822710536</v>
+        <v>506702</v>
       </c>
       <c r="R36" t="n">
-        <v>7114711.854190451</v>
+        <v>7114515</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4689,22 +4448,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,26 +4473,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89595838</v>
+        <v>120141696</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4751,34 +4501,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507248.1943901029</v>
+        <v>506756</v>
       </c>
       <c r="R37" t="n">
-        <v>7114008.921133439</v>
+        <v>7114454</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4805,22 +4555,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4835,26 +4575,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89595676</v>
+        <v>120141691</v>
       </c>
       <c r="B38" t="n">
-        <v>78569</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4887,14 +4623,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506794.0382851731</v>
+        <v>506952</v>
       </c>
       <c r="R38" t="n">
-        <v>7114860.9998238</v>
+        <v>7114997</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4921,22 +4657,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4951,26 +4677,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89595655</v>
+        <v>120141702</v>
       </c>
       <c r="B39" t="n">
-        <v>78569</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4983,34 +4705,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506819.1377885213</v>
+        <v>506729</v>
       </c>
       <c r="R39" t="n">
-        <v>7114771.17331298</v>
+        <v>7114816</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5037,22 +4759,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5067,26 +4779,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89595702</v>
+        <v>120141701</v>
       </c>
       <c r="B40" t="n">
-        <v>78569</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5099,34 +4807,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507245.9293540679</v>
+        <v>506918</v>
       </c>
       <c r="R40" t="n">
-        <v>7114790.03203398</v>
+        <v>7114686</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5153,22 +4861,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5183,26 +4881,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89595651</v>
+        <v>120141692</v>
       </c>
       <c r="B41" t="n">
-        <v>78570</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,34 +4909,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506789.8217948026</v>
+        <v>506954</v>
       </c>
       <c r="R41" t="n">
-        <v>7115189.952818124</v>
+        <v>7115013</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5269,22 +4963,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5299,26 +4983,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>89595686</v>
+        <v>120141706</v>
       </c>
       <c r="B42" t="n">
-        <v>77506</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5351,14 +5031,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506775.9538076027</v>
+        <v>506637</v>
       </c>
       <c r="R42" t="n">
-        <v>7114939.931760079</v>
+        <v>7114645</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5385,22 +5065,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5415,26 +5085,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>89595641</v>
+        <v>120141703</v>
       </c>
       <c r="B43" t="n">
-        <v>78569</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5447,34 +5113,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506781.2047040357</v>
+        <v>506664</v>
       </c>
       <c r="R43" t="n">
-        <v>7114936.016541568</v>
+        <v>7114490</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5501,22 +5167,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5531,26 +5187,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>89595679</v>
+        <v>120141707</v>
       </c>
       <c r="B44" t="n">
-        <v>78569</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5563,34 +5215,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507145.2056182243</v>
+        <v>506822</v>
       </c>
       <c r="R44" t="n">
-        <v>7114705.150157313</v>
+        <v>7114452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5617,22 +5269,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5647,26 +5289,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>89595810</v>
+        <v>120141682</v>
       </c>
       <c r="B45" t="n">
-        <v>89392</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5679,34 +5317,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507192.1324047564</v>
+        <v>506688</v>
       </c>
       <c r="R45" t="n">
-        <v>7114816.085856409</v>
+        <v>7114542</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5733,22 +5371,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5763,26 +5396,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>89595609</v>
+        <v>120141668</v>
       </c>
       <c r="B46" t="n">
-        <v>78569</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5795,34 +5424,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506900.0289812936</v>
+        <v>506672</v>
       </c>
       <c r="R46" t="n">
-        <v>7114740.809616276</v>
+        <v>7114574</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5849,22 +5478,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5879,26 +5498,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>89595634</v>
+        <v>120141700</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
+        <v>57431</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5907,38 +5522,54 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506896.0610483468</v>
+        <v>507032</v>
       </c>
       <c r="R47" t="n">
-        <v>7114756.94492677</v>
+        <v>7114708</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5965,22 +5596,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5995,26 +5616,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118212318</v>
+        <v>120141695</v>
       </c>
       <c r="B48" t="n">
-        <v>90858</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6023,41 +5640,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1506</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjärnen nordan Långtjärnen (Tjärnen nordan Långtjärnen), Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506493</v>
+        <v>506750</v>
       </c>
       <c r="R48" t="n">
-        <v>7114565</v>
+        <v>7114935</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6081,12 +5698,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,22 +5718,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118221783</v>
+        <v>120141675</v>
       </c>
       <c r="B49" t="n">
-        <v>90847</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6125,44 +5742,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507158</v>
+        <v>506831</v>
       </c>
       <c r="R49" t="n">
-        <v>7114884</v>
+        <v>7115012</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6186,17 +5800,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Vidväxt över ulltickan som tidigare var vidväxt under lågan.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6205,75 +5819,71 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118221367</v>
+        <v>120141683</v>
       </c>
       <c r="B50" t="n">
-        <v>91271</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506775</v>
+        <v>507001</v>
       </c>
       <c r="R50" t="n">
-        <v>7115175</v>
+        <v>7114608</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6297,12 +5907,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6311,29 +5926,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141667</v>
+        <v>120141694</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6346,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6370,10 +5984,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506748</v>
+        <v>506824</v>
       </c>
       <c r="R51" t="n">
-        <v>7114878</v>
+        <v>7114993</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6432,10 +6046,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141710</v>
+        <v>120141697</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,21 +6062,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506986</v>
+        <v>506874</v>
       </c>
       <c r="R52" t="n">
-        <v>7114613</v>
+        <v>7114372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6534,7 +6148,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141681</v>
+        <v>120141672</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6574,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506679</v>
+        <v>506895</v>
       </c>
       <c r="R53" t="n">
-        <v>7114465</v>
+        <v>7115116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6614,7 +6228,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6641,7 +6255,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141674</v>
+        <v>120141684</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6681,10 +6295,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506873</v>
+        <v>507001</v>
       </c>
       <c r="R54" t="n">
-        <v>7115121</v>
+        <v>7114716</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6721,7 +6335,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6748,10 +6362,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120141698</v>
+        <v>120141671</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6764,21 +6378,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6402,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506955</v>
+        <v>507102</v>
       </c>
       <c r="R55" t="n">
-        <v>7114545</v>
+        <v>7114733</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6826,6 +6440,11 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6847,3540 +6466,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>120141686</v>
-      </c>
-      <c r="B56" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>506978</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7114547</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>120141673</v>
-      </c>
-      <c r="B57" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>506865</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7115101</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>120141704</v>
-      </c>
-      <c r="B58" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>506731</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7114940</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>120141685</v>
-      </c>
-      <c r="B59" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>506955</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7114545</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>120141666</v>
-      </c>
-      <c r="B60" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>506960</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7115050</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>120141709</v>
-      </c>
-      <c r="B61" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>506840</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7114370</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>120141690</v>
-      </c>
-      <c r="B62" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>506952</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7114935</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>120141699</v>
-      </c>
-      <c r="B63" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>506982</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7114588</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>120141680</v>
-      </c>
-      <c r="B64" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>506703</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7114470</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>120141689</v>
-      </c>
-      <c r="B65" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>506964</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7114937</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>120141688</v>
-      </c>
-      <c r="B66" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>506908</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7114647</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>120141687</v>
-      </c>
-      <c r="B67" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>506979</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7114590</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>120141677</v>
-      </c>
-      <c r="B68" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>506807</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7114959</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>120141705</v>
-      </c>
-      <c r="B69" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>506714</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7114740</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>120141678</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>506702</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7114515</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>120141696</v>
-      </c>
-      <c r="B71" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>506756</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7114454</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>120141691</v>
-      </c>
-      <c r="B72" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>506952</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7114997</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>120141702</v>
-      </c>
-      <c r="B73" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>506729</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7114816</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>120141701</v>
-      </c>
-      <c r="B74" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>506918</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7114686</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>120141692</v>
-      </c>
-      <c r="B75" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>506954</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7115013</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>120141706</v>
-      </c>
-      <c r="B76" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>506637</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7114645</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>120141703</v>
-      </c>
-      <c r="B77" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>506664</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7114490</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>120141707</v>
-      </c>
-      <c r="B78" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>506822</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7114452</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>120141682</v>
-      </c>
-      <c r="B79" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>506688</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7114542</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>120141668</v>
-      </c>
-      <c r="B80" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>506672</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7114574</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>120141700</v>
-      </c>
-      <c r="B81" t="n">
-        <v>57431</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>507032</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7114708</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>120141695</v>
-      </c>
-      <c r="B82" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>506750</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7114935</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>120141675</v>
-      </c>
-      <c r="B83" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>506831</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7115012</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>120141683</v>
-      </c>
-      <c r="B84" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>507001</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7114608</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>120141694</v>
-      </c>
-      <c r="B85" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>506824</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7114993</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>120141697</v>
-      </c>
-      <c r="B86" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>506874</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7114372</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>120141672</v>
-      </c>
-      <c r="B87" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>506895</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7115116</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>120141684</v>
-      </c>
-      <c r="B88" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>507001</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7114716</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>120141671</v>
-      </c>
-      <c r="B89" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>507102</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7114733</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89595656</v>
+        <v>120141666</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506775.9538076027</v>
+        <v>506960</v>
       </c>
       <c r="R2" t="n">
-        <v>7114939.931760079</v>
+        <v>7115050</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89595660</v>
+        <v>120141667</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506809.9699894598</v>
+        <v>506748</v>
       </c>
       <c r="R3" t="n">
-        <v>7114768.09885634</v>
+        <v>7114878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89595663</v>
+        <v>120141668</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507036.7971198635</v>
+        <v>506672</v>
       </c>
       <c r="R4" t="n">
-        <v>7114731.081843849</v>
+        <v>7114574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89595669</v>
+        <v>89595618</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506897.8464952148</v>
+        <v>506819</v>
       </c>
       <c r="R5" t="n">
-        <v>7114739.93209392</v>
+        <v>7114771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1034,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89595636</v>
+        <v>89595633</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506781.2047040357</v>
+        <v>506793</v>
       </c>
       <c r="R6" t="n">
-        <v>7114936.016541568</v>
+        <v>7114856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1135,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89595633</v>
+        <v>89595635</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506793.1750779065</v>
+        <v>506776</v>
       </c>
       <c r="R7" t="n">
-        <v>7114856.198487628</v>
+        <v>7114940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1236,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89595635</v>
+        <v>89595636</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506775.9538076027</v>
+        <v>506781</v>
       </c>
       <c r="R8" t="n">
-        <v>7114939.931760079</v>
+        <v>7114936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1337,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89595618</v>
+        <v>89595669</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506819.1377885213</v>
+        <v>506898</v>
       </c>
       <c r="R9" t="n">
-        <v>7114771.17331298</v>
+        <v>7114740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1438,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89595668</v>
+        <v>89595684</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506781.0679131226</v>
+        <v>506745</v>
       </c>
       <c r="R10" t="n">
-        <v>7114799.014384815</v>
+        <v>7114995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1539,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,15 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89595676</v>
+        <v>120141685</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,34 +1583,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506794.0382851731</v>
+        <v>506955</v>
       </c>
       <c r="R11" t="n">
-        <v>7114860.9998238</v>
+        <v>7114545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,22 +1637,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,31 +1657,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89595655</v>
+        <v>120141686</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,34 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506819.1377885213</v>
+        <v>506978</v>
       </c>
       <c r="R12" t="n">
-        <v>7114771.17331298</v>
+        <v>7114547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,22 +1734,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,31 +1754,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89595686</v>
+        <v>120141687</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,34 +1777,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhögen, Jmt</t>
+          <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506775.9538076027</v>
+        <v>506979</v>
       </c>
       <c r="R13" t="n">
-        <v>7114939.931760079</v>
+        <v>7114590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,22 +1831,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,53 +1851,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89595641</v>
+        <v>89595634</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506781.2047040357</v>
+        <v>506896</v>
       </c>
       <c r="R14" t="n">
-        <v>7114936.016541568</v>
+        <v>7114757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +1931,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,37 +1964,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89595609</v>
+        <v>89595663</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506900.0289812936</v>
+        <v>507037</v>
       </c>
       <c r="R15" t="n">
-        <v>7114740.809616276</v>
+        <v>7114731</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,19 +2032,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,19 +2065,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89595634</v>
+        <v>89595686</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2339,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506896.0610483468</v>
+        <v>506776</v>
       </c>
       <c r="R16" t="n">
-        <v>7114756.94492677</v>
+        <v>7114940</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,19 +2133,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,37 +2166,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120141667</v>
+        <v>120141704</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506748</v>
+        <v>506731</v>
       </c>
       <c r="R17" t="n">
-        <v>7114878</v>
+        <v>7114940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,19 +2263,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120141710</v>
+        <v>120141705</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2557,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506986</v>
+        <v>506714</v>
       </c>
       <c r="R18" t="n">
-        <v>7114613</v>
+        <v>7114740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2619,37 +2360,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120141681</v>
+        <v>120141706</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2659,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506679</v>
+        <v>506637</v>
       </c>
       <c r="R19" t="n">
-        <v>7114465</v>
+        <v>7114645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,11 +2431,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,37 +2457,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120141674</v>
+        <v>120141707</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506873</v>
+        <v>506822</v>
       </c>
       <c r="R20" t="n">
-        <v>7115121</v>
+        <v>7114452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,11 +2528,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,37 +2554,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120141698</v>
+        <v>120141709</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2873,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506955</v>
+        <v>506840</v>
       </c>
       <c r="R21" t="n">
-        <v>7114545</v>
+        <v>7114370</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,37 +2651,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120141686</v>
+        <v>120141710</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2686,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506978</v>
+        <v>506986</v>
       </c>
       <c r="R22" t="n">
-        <v>7114547</v>
+        <v>7114613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3037,15 +2748,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120141673</v>
+        <v>89595609</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,34 +2759,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506865</v>
+        <v>506900</v>
       </c>
       <c r="R23" t="n">
-        <v>7115101</v>
+        <v>7114741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3107,17 +2813,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,27 +2833,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120141704</v>
+        <v>89595641</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,34 +2860,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506731</v>
+        <v>506781</v>
       </c>
       <c r="R24" t="n">
-        <v>7114940</v>
+        <v>7114936</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,12 +2914,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,27 +2934,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120141685</v>
+        <v>89595649</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,34 +2961,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506955</v>
+        <v>506745</v>
       </c>
       <c r="R25" t="n">
-        <v>7114545</v>
+        <v>7114995</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3316,12 +3015,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3336,27 +3035,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120141666</v>
+        <v>89595655</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,34 +3062,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506960</v>
+        <v>506819</v>
       </c>
       <c r="R26" t="n">
-        <v>7115050</v>
+        <v>7114771</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3418,12 +3116,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3438,27 +3136,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120141709</v>
+        <v>89595656</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,34 +3163,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506840</v>
+        <v>506776</v>
       </c>
       <c r="R27" t="n">
-        <v>7114370</v>
+        <v>7114940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3520,12 +3217,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3540,27 +3237,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120141690</v>
+        <v>89595660</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3588,14 +3284,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506952</v>
+        <v>506810</v>
       </c>
       <c r="R28" t="n">
-        <v>7114935</v>
+        <v>7114768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3622,12 +3318,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,27 +3338,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120141699</v>
+        <v>89595668</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3690,14 +3385,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506982</v>
+        <v>506781</v>
       </c>
       <c r="R29" t="n">
-        <v>7114588</v>
+        <v>7114799</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3724,12 +3419,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3744,27 +3439,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120141680</v>
+        <v>89595676</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3772,34 +3466,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-rishögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506703</v>
+        <v>506794</v>
       </c>
       <c r="R30" t="n">
-        <v>7114470</v>
+        <v>7114861</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3826,17 +3520,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3851,27 +3540,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120141689</v>
+        <v>120141688</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3903,10 +3591,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506964</v>
+        <v>506908</v>
       </c>
       <c r="R31" t="n">
-        <v>7114937</v>
+        <v>7114647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3965,15 +3653,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120141688</v>
+        <v>120141689</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,10 +3688,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506908</v>
+        <v>506964</v>
       </c>
       <c r="R32" t="n">
-        <v>7114647</v>
+        <v>7114937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,15 +3750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120141687</v>
+        <v>120141690</v>
       </c>
       <c r="B33" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,21 +3761,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,10 +3785,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506979</v>
+        <v>506952</v>
       </c>
       <c r="R33" t="n">
-        <v>7114590</v>
+        <v>7114935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,15 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120141677</v>
+        <v>120141691</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4185,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4209,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506807</v>
+        <v>506952</v>
       </c>
       <c r="R34" t="n">
-        <v>7114959</v>
+        <v>7114997</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,11 +3918,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4276,15 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120141705</v>
+        <v>120141692</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4292,21 +3955,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4316,10 +3979,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506714</v>
+        <v>506954</v>
       </c>
       <c r="R35" t="n">
-        <v>7114740</v>
+        <v>7115013</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,15 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120141678</v>
+        <v>120141694</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4394,21 +4052,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4418,10 +4076,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506702</v>
+        <v>506824</v>
       </c>
       <c r="R36" t="n">
-        <v>7114515</v>
+        <v>7114993</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4454,11 +4112,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4485,15 +4138,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120141696</v>
+        <v>120141695</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,10 +4173,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506756</v>
+        <v>506750</v>
       </c>
       <c r="R37" t="n">
-        <v>7114454</v>
+        <v>7114935</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4587,15 +4235,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120141691</v>
+        <v>120141696</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,10 +4270,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506952</v>
+        <v>506756</v>
       </c>
       <c r="R38" t="n">
-        <v>7114997</v>
+        <v>7114454</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4689,15 +4332,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120141702</v>
+        <v>120141697</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,21 +4343,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4729,10 +4367,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506729</v>
+        <v>506874</v>
       </c>
       <c r="R39" t="n">
-        <v>7114816</v>
+        <v>7114372</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4791,15 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120141701</v>
+        <v>120141698</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4807,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4831,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506918</v>
+        <v>506955</v>
       </c>
       <c r="R40" t="n">
-        <v>7114686</v>
+        <v>7114545</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4893,15 +4526,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120141692</v>
+        <v>120141699</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506954</v>
+        <v>506982</v>
       </c>
       <c r="R41" t="n">
-        <v>7115013</v>
+        <v>7114588</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4995,15 +4623,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120141706</v>
+        <v>120141671</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,21 +4634,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5035,10 +4658,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506637</v>
+        <v>507102</v>
       </c>
       <c r="R42" t="n">
-        <v>7114645</v>
+        <v>7114733</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5071,6 +4694,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5097,15 +4725,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120141703</v>
+        <v>120141672</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5113,21 +4736,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5137,10 +4760,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506664</v>
+        <v>506895</v>
       </c>
       <c r="R43" t="n">
-        <v>7114490</v>
+        <v>7115116</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5173,6 +4796,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5199,15 +4827,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120141707</v>
+        <v>120141673</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,21 +4838,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +4862,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506822</v>
+        <v>506865</v>
       </c>
       <c r="R44" t="n">
-        <v>7114452</v>
+        <v>7115101</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,6 +4898,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,15 +4929,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120141682</v>
+        <v>120141674</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,10 +4964,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506688</v>
+        <v>506873</v>
       </c>
       <c r="R45" t="n">
-        <v>7114542</v>
+        <v>7115121</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5004,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5408,15 +5031,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120141668</v>
+        <v>120141675</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,21 +5042,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5448,10 +5066,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506672</v>
+        <v>506831</v>
       </c>
       <c r="R46" t="n">
-        <v>7114574</v>
+        <v>7115012</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,6 +5102,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,32 +5133,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120141700</v>
+        <v>120141677</v>
       </c>
       <c r="B47" t="n">
-        <v>57431</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5543,33 +5161,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507032</v>
+        <v>506807</v>
       </c>
       <c r="R47" t="n">
-        <v>7114708</v>
+        <v>7114959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5602,6 +5204,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,15 +5235,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120141695</v>
+        <v>120141678</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5644,21 +5246,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5668,10 +5270,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506750</v>
+        <v>506702</v>
       </c>
       <c r="R48" t="n">
-        <v>7114935</v>
+        <v>7114515</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5704,6 +5306,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5730,15 +5337,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120141675</v>
+        <v>120141680</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5770,10 +5372,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506831</v>
+        <v>506703</v>
       </c>
       <c r="R49" t="n">
-        <v>7115012</v>
+        <v>7114470</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5810,7 +5412,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,15 +5439,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120141683</v>
+        <v>120141681</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,10 +5474,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507001</v>
+        <v>506679</v>
       </c>
       <c r="R50" t="n">
-        <v>7114608</v>
+        <v>7114465</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5917,7 +5514,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5944,15 +5541,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120141694</v>
+        <v>120141682</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5552,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5984,10 +5576,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506824</v>
+        <v>506688</v>
       </c>
       <c r="R51" t="n">
-        <v>7114993</v>
+        <v>7114542</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6020,6 +5612,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6046,15 +5643,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120141697</v>
+        <v>120141683</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6062,21 +5654,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +5678,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506874</v>
+        <v>507001</v>
       </c>
       <c r="R52" t="n">
-        <v>7114372</v>
+        <v>7114608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6122,6 +5714,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6148,15 +5745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120141672</v>
+        <v>120141684</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6188,10 +5780,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506895</v>
+        <v>507001</v>
       </c>
       <c r="R53" t="n">
-        <v>7115116</v>
+        <v>7114716</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6228,7 +5820,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6255,15 +5847,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120141684</v>
+        <v>120141700</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6271,16 +5858,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6288,17 +5875,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-rishögen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507001</v>
+        <v>507032</v>
       </c>
       <c r="R54" t="n">
-        <v>7114716</v>
+        <v>7114708</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6333,11 +5936,6 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6359,113 +5957,6 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>120141671</v>
-      </c>
-      <c r="B55" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Stor-rishögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>507102</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7114733</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60761-2023 artfynd.xlsx
+++ b/artfynd/A 60761-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141667</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595633</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595636</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595684</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141685</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141686</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141687</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595634</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595663</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595686</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141704</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141705</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141707</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2648,6 +2748,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141709</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2745,6 +2850,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141710</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2846,6 +2956,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595609</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2947,6 +3062,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595641</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3048,6 +3168,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595649</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595655</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3250,6 +3380,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595656</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3351,6 +3486,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595660</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3452,6 +3592,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595668</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3553,6 +3698,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595676</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3650,6 +3800,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141688</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3747,6 +3902,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141689</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3844,6 +4004,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141690</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3941,6 +4106,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141691</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4038,6 +4208,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141692</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4135,6 +4310,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141694</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4232,6 +4412,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141695</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4329,6 +4514,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141696</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4426,6 +4616,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141697</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4523,6 +4718,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141698</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4620,6 +4820,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141699</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4722,6 +4927,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141671</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4824,6 +5034,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141672</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4926,6 +5141,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141673</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5028,6 +5248,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141674</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5130,6 +5355,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141675</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5232,6 +5462,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141677</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5334,6 +5569,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141678</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5436,6 +5676,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141680</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5538,6 +5783,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141681</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5640,6 +5890,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141682</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5742,6 +5997,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141683</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5844,6 +6104,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141684</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5957,8 +6222,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120141700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>